--- a/data/aqi_monthly_new.xlsx
+++ b/data/aqi_monthly_new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chris/Documents/Codex/city aqi trend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8B6FB1-B370-9F48-A540-2FEE9877FB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A22BB56-67AA-4546-9635-71F5367092FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="3260" windowWidth="27640" windowHeight="16860" xr2:uid="{D7222D1B-867A-AD4E-9CAA-08BD12F37CC0}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3662" uniqueCount="1121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4133" uniqueCount="1243">
   <si>
     <t>月份</t>
   </si>
@@ -3406,6 +3406,373 @@
   </si>
   <si>
     <t>芜湖</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>48~111</t>
+  </si>
+  <si>
+    <t>42~85</t>
+  </si>
+  <si>
+    <t>32~85</t>
+  </si>
+  <si>
+    <t>32~62</t>
+  </si>
+  <si>
+    <t>57~167</t>
+  </si>
+  <si>
+    <t>57~158</t>
+  </si>
+  <si>
+    <t>68~305</t>
+  </si>
+  <si>
+    <t>102~360</t>
+  </si>
+  <si>
+    <t>39~230</t>
+  </si>
+  <si>
+    <t>57~156</t>
+  </si>
+  <si>
+    <t>52~263</t>
+  </si>
+  <si>
+    <t>36~186</t>
+  </si>
+  <si>
+    <t>26~183</t>
+  </si>
+  <si>
+    <t>54~249</t>
+  </si>
+  <si>
+    <t>57~366</t>
+  </si>
+  <si>
+    <t>57~201</t>
+  </si>
+  <si>
+    <t>72~272</t>
+  </si>
+  <si>
+    <t>63~203</t>
+  </si>
+  <si>
+    <t>67~244</t>
+  </si>
+  <si>
+    <t>60~152</t>
+  </si>
+  <si>
+    <t>62~237</t>
+  </si>
+  <si>
+    <t>28~145</t>
+  </si>
+  <si>
+    <t>40~111</t>
+  </si>
+  <si>
+    <t>40~214</t>
+  </si>
+  <si>
+    <t>38~186</t>
+  </si>
+  <si>
+    <t>50~341</t>
+  </si>
+  <si>
+    <t>63~367</t>
+  </si>
+  <si>
+    <t>47~240</t>
+  </si>
+  <si>
+    <t>49~198</t>
+  </si>
+  <si>
+    <t>29~120</t>
+  </si>
+  <si>
+    <t>30~118</t>
+  </si>
+  <si>
+    <t>44~132</t>
+  </si>
+  <si>
+    <t>30~112</t>
+  </si>
+  <si>
+    <t>33~267</t>
+  </si>
+  <si>
+    <t>68~389</t>
+  </si>
+  <si>
+    <t>0~226</t>
+  </si>
+  <si>
+    <t>0~172</t>
+  </si>
+  <si>
+    <t>0~108</t>
+  </si>
+  <si>
+    <t>0~138</t>
+  </si>
+  <si>
+    <t>27~134</t>
+  </si>
+  <si>
+    <t>29~142</t>
+  </si>
+  <si>
+    <t>29~152</t>
+  </si>
+  <si>
+    <t>0~230</t>
+  </si>
+  <si>
+    <t>0~346</t>
+  </si>
+  <si>
+    <t>0~234</t>
+  </si>
+  <si>
+    <t>0~129</t>
+  </si>
+  <si>
+    <t>0~153</t>
+  </si>
+  <si>
+    <t>30~130</t>
+  </si>
+  <si>
+    <t>35~163</t>
+  </si>
+  <si>
+    <t>0~170</t>
+  </si>
+  <si>
+    <t>0~312</t>
+  </si>
+  <si>
+    <t>74~316</t>
+  </si>
+  <si>
+    <t>60~179</t>
+  </si>
+  <si>
+    <t>56~124</t>
+  </si>
+  <si>
+    <t>0~122</t>
+  </si>
+  <si>
+    <t>52~126</t>
+  </si>
+  <si>
+    <t>31~159</t>
+  </si>
+  <si>
+    <t>54~196</t>
+  </si>
+  <si>
+    <t>53~229</t>
+  </si>
+  <si>
+    <t>32~182</t>
+  </si>
+  <si>
+    <t>49~139</t>
+  </si>
+  <si>
+    <t>43~124</t>
+  </si>
+  <si>
+    <t>34~99</t>
+  </si>
+  <si>
+    <t>31~94</t>
+  </si>
+  <si>
+    <t>26~120</t>
+  </si>
+  <si>
+    <t>37~119</t>
+  </si>
+  <si>
+    <t>38~110</t>
+  </si>
+  <si>
+    <t>37~132</t>
+  </si>
+  <si>
+    <t>40~165</t>
+  </si>
+  <si>
+    <t>56~288</t>
+  </si>
+  <si>
+    <t>53~139</t>
+  </si>
+  <si>
+    <t>42~500</t>
+  </si>
+  <si>
+    <t>37~162</t>
+  </si>
+  <si>
+    <t>29~98</t>
+  </si>
+  <si>
+    <t>31~85</t>
+  </si>
+  <si>
+    <t>37~81</t>
+  </si>
+  <si>
+    <t>29~119</t>
+  </si>
+  <si>
+    <t>19~144</t>
+  </si>
+  <si>
+    <t>36~202</t>
+  </si>
+  <si>
+    <t>49~195</t>
+  </si>
+  <si>
+    <t>52~244</t>
+  </si>
+  <si>
+    <t>31~167</t>
+  </si>
+  <si>
+    <t>49~110</t>
+  </si>
+  <si>
+    <t>48~124</t>
+  </si>
+  <si>
+    <t>27~142</t>
+  </si>
+  <si>
+    <t>33~95</t>
+  </si>
+  <si>
+    <t>28~97</t>
+  </si>
+  <si>
+    <t>51~120</t>
+  </si>
+  <si>
+    <t>26~163</t>
+  </si>
+  <si>
+    <t>44~198</t>
+  </si>
+  <si>
+    <t>39~294</t>
+  </si>
+  <si>
+    <t>30~210</t>
+  </si>
+  <si>
+    <t>33~491</t>
+  </si>
+  <si>
+    <t>25~103</t>
+  </si>
+  <si>
+    <t>40~136</t>
+  </si>
+  <si>
+    <t>45~101</t>
+  </si>
+  <si>
+    <t>32~90</t>
+  </si>
+  <si>
+    <t>38~104</t>
+  </si>
+  <si>
+    <t>38~259</t>
+  </si>
+  <si>
+    <t>51~229</t>
+  </si>
+  <si>
+    <t>34~162</t>
+  </si>
+  <si>
+    <t>40~155</t>
+  </si>
+  <si>
+    <t>43~107</t>
+  </si>
+  <si>
+    <t>51~134</t>
+  </si>
+  <si>
+    <t>29~82</t>
+  </si>
+  <si>
+    <t>31~107</t>
+  </si>
+  <si>
+    <t>32~120</t>
+  </si>
+  <si>
+    <t>32~127</t>
+  </si>
+  <si>
+    <t>46~175</t>
+  </si>
+  <si>
+    <t>49~241</t>
+  </si>
+  <si>
+    <t>44~169</t>
+  </si>
+  <si>
+    <t>33~85</t>
+  </si>
+  <si>
+    <t>23~74</t>
+  </si>
+  <si>
+    <t>18~94</t>
+  </si>
+  <si>
+    <t>22~124</t>
+  </si>
+  <si>
+    <t>52~224</t>
+  </si>
+  <si>
+    <t>44~179</t>
+  </si>
+  <si>
+    <t>39~137</t>
+  </si>
+  <si>
+    <t>34~141</t>
+  </si>
+  <si>
+    <t>31~90</t>
+  </si>
+  <si>
+    <t>22~90</t>
+  </si>
+  <si>
+    <t>信阳</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -3832,7 +4199,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9733C82F-3F42-DA44-A321-4ADA684D9E78}">
-  <dimension ref="A1:K1218"/>
+  <dimension ref="A1:K1375"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="14.83203125" style="7" customWidth="1"/>
@@ -46468,6 +46835,5501 @@
       </c>
       <c r="K1218" s="2">
         <v>129</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:11" ht="18">
+      <c r="A1219" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1219" s="6">
+        <v>41395</v>
+      </c>
+      <c r="C1219" s="2">
+        <v>77</v>
+      </c>
+      <c r="D1219" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E1219" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1219" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1219" s="2">
+        <v>103</v>
+      </c>
+      <c r="H1219" s="2">
+        <v>23</v>
+      </c>
+      <c r="I1219" s="2">
+        <v>30</v>
+      </c>
+      <c r="J1219" s="2">
+        <v>0</v>
+      </c>
+      <c r="K1219" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:11" ht="18">
+      <c r="A1220" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1220" s="6">
+        <v>41426</v>
+      </c>
+      <c r="C1220" s="2">
+        <v>61</v>
+      </c>
+      <c r="D1220" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E1220" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1220" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1220" s="2">
+        <v>72</v>
+      </c>
+      <c r="H1220" s="2">
+        <v>21</v>
+      </c>
+      <c r="I1220" s="2">
+        <v>40</v>
+      </c>
+      <c r="J1220" s="2">
+        <v>0</v>
+      </c>
+      <c r="K1220" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:11" ht="18">
+      <c r="A1221" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1221" s="6">
+        <v>41456</v>
+      </c>
+      <c r="C1221" s="2">
+        <v>51</v>
+      </c>
+      <c r="D1221" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E1221" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1221" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1221" s="2">
+        <v>53</v>
+      </c>
+      <c r="H1221" s="2">
+        <v>20</v>
+      </c>
+      <c r="I1221" s="2">
+        <v>34</v>
+      </c>
+      <c r="J1221" s="2">
+        <v>0</v>
+      </c>
+      <c r="K1221" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:11" ht="18">
+      <c r="A1222" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1222" s="6">
+        <v>41487</v>
+      </c>
+      <c r="C1222" s="2">
+        <v>42</v>
+      </c>
+      <c r="D1222" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E1222" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1222" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1222" s="2">
+        <v>40</v>
+      </c>
+      <c r="H1222" s="2">
+        <v>18</v>
+      </c>
+      <c r="I1222" s="2">
+        <v>35</v>
+      </c>
+      <c r="J1222" s="2">
+        <v>0</v>
+      </c>
+      <c r="K1222" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:11" ht="18">
+      <c r="A1223" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1223" s="6">
+        <v>41518</v>
+      </c>
+      <c r="C1223" s="2">
+        <v>64</v>
+      </c>
+      <c r="D1223" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="E1223" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1223" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1223" s="2">
+        <v>76</v>
+      </c>
+      <c r="H1223" s="2">
+        <v>22</v>
+      </c>
+      <c r="I1223" s="2">
+        <v>38</v>
+      </c>
+      <c r="J1223" s="2">
+        <v>0</v>
+      </c>
+      <c r="K1223" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:11" ht="18">
+      <c r="A1224" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1224" s="6">
+        <v>41548</v>
+      </c>
+      <c r="C1224" s="2">
+        <v>96</v>
+      </c>
+      <c r="D1224" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E1224" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1224" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1224" s="2">
+        <v>142</v>
+      </c>
+      <c r="H1224" s="2">
+        <v>36</v>
+      </c>
+      <c r="I1224" s="2">
+        <v>56</v>
+      </c>
+      <c r="J1224" s="2">
+        <v>0</v>
+      </c>
+      <c r="K1224" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:11" ht="18">
+      <c r="A1225" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1225" s="6">
+        <v>41579</v>
+      </c>
+      <c r="C1225" s="2">
+        <v>91</v>
+      </c>
+      <c r="D1225" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E1225" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1225" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1225" s="2">
+        <v>125</v>
+      </c>
+      <c r="H1225" s="2">
+        <v>45</v>
+      </c>
+      <c r="I1225" s="2">
+        <v>44</v>
+      </c>
+      <c r="J1225" s="2">
+        <v>0</v>
+      </c>
+      <c r="K1225" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:11" ht="18">
+      <c r="A1226" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1226" s="6">
+        <v>41609</v>
+      </c>
+      <c r="C1226" s="2">
+        <v>154</v>
+      </c>
+      <c r="D1226" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1226" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1226" s="2">
+        <v>102</v>
+      </c>
+      <c r="G1226" s="2">
+        <v>184</v>
+      </c>
+      <c r="H1226" s="2">
+        <v>57</v>
+      </c>
+      <c r="I1226" s="2">
+        <v>61</v>
+      </c>
+      <c r="J1226" s="2">
+        <v>1.403</v>
+      </c>
+      <c r="K1226" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:11" ht="18">
+      <c r="A1227" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1227" s="6">
+        <v>41640</v>
+      </c>
+      <c r="C1227" s="2">
+        <v>205</v>
+      </c>
+      <c r="D1227" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E1227" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1227" s="2">
+        <v>161</v>
+      </c>
+      <c r="G1227" s="2">
+        <v>221</v>
+      </c>
+      <c r="H1227" s="2">
+        <v>60</v>
+      </c>
+      <c r="I1227" s="2">
+        <v>58</v>
+      </c>
+      <c r="J1227" s="2">
+        <v>1.5680000000000001</v>
+      </c>
+      <c r="K1227" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:11" ht="18">
+      <c r="A1228" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1228" s="6">
+        <v>41671</v>
+      </c>
+      <c r="C1228" s="2">
+        <v>106</v>
+      </c>
+      <c r="D1228" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E1228" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1228" s="2">
+        <v>71</v>
+      </c>
+      <c r="G1228" s="2">
+        <v>99</v>
+      </c>
+      <c r="H1228" s="2">
+        <v>31</v>
+      </c>
+      <c r="I1228" s="2">
+        <v>30</v>
+      </c>
+      <c r="J1228" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="K1228" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:11" ht="18">
+      <c r="A1229" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1229" s="6">
+        <v>41699</v>
+      </c>
+      <c r="C1229" s="2">
+        <v>106</v>
+      </c>
+      <c r="D1229" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E1229" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1229" s="2">
+        <v>76</v>
+      </c>
+      <c r="G1229" s="2">
+        <v>124</v>
+      </c>
+      <c r="H1229" s="2">
+        <v>37</v>
+      </c>
+      <c r="I1229" s="2">
+        <v>35</v>
+      </c>
+      <c r="J1229" s="2">
+        <v>0.89</v>
+      </c>
+      <c r="K1229" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:11" ht="18">
+      <c r="A1230" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1230" s="6">
+        <v>41730</v>
+      </c>
+      <c r="C1230" s="2">
+        <v>98</v>
+      </c>
+      <c r="D1230" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E1230" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1230" s="2">
+        <v>59</v>
+      </c>
+      <c r="G1230" s="2">
+        <v>96</v>
+      </c>
+      <c r="H1230" s="2">
+        <v>28</v>
+      </c>
+      <c r="I1230" s="2">
+        <v>29</v>
+      </c>
+      <c r="J1230" s="2">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="K1230" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:11" ht="18">
+      <c r="A1231" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1231" s="6">
+        <v>41760</v>
+      </c>
+      <c r="C1231" s="2">
+        <v>112</v>
+      </c>
+      <c r="D1231" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E1231" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1231" s="2">
+        <v>70</v>
+      </c>
+      <c r="G1231" s="2">
+        <v>126</v>
+      </c>
+      <c r="H1231" s="2">
+        <v>21</v>
+      </c>
+      <c r="I1231" s="2">
+        <v>25</v>
+      </c>
+      <c r="J1231" s="2">
+        <v>0.51900000000000002</v>
+      </c>
+      <c r="K1231" s="2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:11" ht="18">
+      <c r="A1232" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1232" s="6">
+        <v>41791</v>
+      </c>
+      <c r="C1232" s="2">
+        <v>130</v>
+      </c>
+      <c r="D1232" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E1232" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1232" s="2">
+        <v>84</v>
+      </c>
+      <c r="G1232" s="2">
+        <v>94</v>
+      </c>
+      <c r="H1232" s="2">
+        <v>19</v>
+      </c>
+      <c r="I1232" s="2">
+        <v>11</v>
+      </c>
+      <c r="J1232" s="2">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="K1232" s="2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:11" ht="18">
+      <c r="A1233" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1233" s="6">
+        <v>41821</v>
+      </c>
+      <c r="C1233" s="2">
+        <v>84</v>
+      </c>
+      <c r="D1233" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E1233" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1233" s="2">
+        <v>52</v>
+      </c>
+      <c r="G1233" s="2">
+        <v>76</v>
+      </c>
+      <c r="H1233" s="2">
+        <v>15</v>
+      </c>
+      <c r="I1233" s="2">
+        <v>15</v>
+      </c>
+      <c r="J1233" s="2">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="K1233" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:11" ht="18">
+      <c r="A1234" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1234" s="6">
+        <v>41852</v>
+      </c>
+      <c r="C1234" s="2">
+        <v>84</v>
+      </c>
+      <c r="D1234" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1234" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1234" s="2">
+        <v>57</v>
+      </c>
+      <c r="G1234" s="2">
+        <v>88</v>
+      </c>
+      <c r="H1234" s="2">
+        <v>26</v>
+      </c>
+      <c r="I1234" s="2">
+        <v>26</v>
+      </c>
+      <c r="J1234" s="2">
+        <v>0.59699999999999998</v>
+      </c>
+      <c r="K1234" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:11" ht="18">
+      <c r="A1235" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1235" s="6">
+        <v>41883</v>
+      </c>
+      <c r="C1235" s="2">
+        <v>82</v>
+      </c>
+      <c r="D1235" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E1235" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1235" s="2">
+        <v>54</v>
+      </c>
+      <c r="G1235" s="2">
+        <v>79</v>
+      </c>
+      <c r="H1235" s="2">
+        <v>23</v>
+      </c>
+      <c r="I1235" s="2">
+        <v>20</v>
+      </c>
+      <c r="J1235" s="2">
+        <v>0.753</v>
+      </c>
+      <c r="K1235" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:11" ht="18">
+      <c r="A1236" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1236" s="6">
+        <v>41913</v>
+      </c>
+      <c r="C1236" s="2">
+        <v>125</v>
+      </c>
+      <c r="D1236" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E1236" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1236" s="2">
+        <v>92</v>
+      </c>
+      <c r="G1236" s="2">
+        <v>135</v>
+      </c>
+      <c r="H1236" s="2">
+        <v>33</v>
+      </c>
+      <c r="I1236" s="2">
+        <v>21</v>
+      </c>
+      <c r="J1236" s="2">
+        <v>0.79400000000000004</v>
+      </c>
+      <c r="K1236" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:11" ht="18">
+      <c r="A1237" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1237" s="6">
+        <v>41944</v>
+      </c>
+      <c r="C1237" s="2">
+        <v>112</v>
+      </c>
+      <c r="D1237" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E1237" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1237" s="2">
+        <v>82</v>
+      </c>
+      <c r="G1237" s="2">
+        <v>127</v>
+      </c>
+      <c r="H1237" s="2">
+        <v>43</v>
+      </c>
+      <c r="I1237" s="2">
+        <v>21</v>
+      </c>
+      <c r="J1237" s="2">
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="K1237" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:11" ht="18">
+      <c r="A1238" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1238" s="6">
+        <v>41974</v>
+      </c>
+      <c r="C1238" s="2">
+        <v>104</v>
+      </c>
+      <c r="D1238" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E1238" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1238" s="2">
+        <v>70</v>
+      </c>
+      <c r="G1238" s="2">
+        <v>135</v>
+      </c>
+      <c r="H1238" s="2">
+        <v>40</v>
+      </c>
+      <c r="I1238" s="2">
+        <v>34</v>
+      </c>
+      <c r="J1238" s="2">
+        <v>0.86799999999999999</v>
+      </c>
+      <c r="K1238" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:11" ht="18">
+      <c r="A1239" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1239" s="6">
+        <v>42005</v>
+      </c>
+      <c r="C1239" s="2">
+        <v>150</v>
+      </c>
+      <c r="D1239" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E1239" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1239" s="2">
+        <v>115</v>
+      </c>
+      <c r="G1239" s="2">
+        <v>170</v>
+      </c>
+      <c r="H1239" s="2">
+        <v>52</v>
+      </c>
+      <c r="I1239" s="2">
+        <v>31</v>
+      </c>
+      <c r="J1239" s="2">
+        <v>1.181</v>
+      </c>
+      <c r="K1239" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:11" ht="18">
+      <c r="A1240" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1240" s="6">
+        <v>42036</v>
+      </c>
+      <c r="C1240" s="2">
+        <v>128</v>
+      </c>
+      <c r="D1240" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E1240" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1240" s="2">
+        <v>93</v>
+      </c>
+      <c r="G1240" s="2">
+        <v>156</v>
+      </c>
+      <c r="H1240" s="2">
+        <v>40</v>
+      </c>
+      <c r="I1240" s="2">
+        <v>25</v>
+      </c>
+      <c r="J1240" s="2">
+        <v>1.018</v>
+      </c>
+      <c r="K1240" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:11" ht="18">
+      <c r="A1241" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1241" s="6">
+        <v>42064</v>
+      </c>
+      <c r="C1241" s="2">
+        <v>102</v>
+      </c>
+      <c r="D1241" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E1241" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1241" s="2">
+        <v>71</v>
+      </c>
+      <c r="G1241" s="2">
+        <v>123</v>
+      </c>
+      <c r="H1241" s="2">
+        <v>31</v>
+      </c>
+      <c r="I1241" s="2">
+        <v>19</v>
+      </c>
+      <c r="J1241" s="2">
+        <v>0.81299999999999994</v>
+      </c>
+      <c r="K1241" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:11" ht="18">
+      <c r="A1242" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1242" s="6">
+        <v>42095</v>
+      </c>
+      <c r="C1242" s="2">
+        <v>98</v>
+      </c>
+      <c r="D1242" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E1242" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1242" s="2">
+        <v>64</v>
+      </c>
+      <c r="G1242" s="2">
+        <v>100</v>
+      </c>
+      <c r="H1242" s="2">
+        <v>29</v>
+      </c>
+      <c r="I1242" s="2">
+        <v>17</v>
+      </c>
+      <c r="J1242" s="2">
+        <v>0.71</v>
+      </c>
+      <c r="K1242" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:11" ht="18">
+      <c r="A1243" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1243" s="6">
+        <v>42125</v>
+      </c>
+      <c r="C1243" s="2">
+        <v>119</v>
+      </c>
+      <c r="D1243" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E1243" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1243" s="2">
+        <v>85</v>
+      </c>
+      <c r="G1243" s="2">
+        <v>127</v>
+      </c>
+      <c r="H1243" s="2">
+        <v>20</v>
+      </c>
+      <c r="I1243" s="2">
+        <v>16</v>
+      </c>
+      <c r="J1243" s="2">
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="K1243" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:11" ht="18">
+      <c r="A1244" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1244" s="6">
+        <v>42156</v>
+      </c>
+      <c r="C1244" s="2">
+        <v>78</v>
+      </c>
+      <c r="D1244" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E1244" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1244" s="2">
+        <v>47</v>
+      </c>
+      <c r="G1244" s="2">
+        <v>80</v>
+      </c>
+      <c r="H1244" s="2">
+        <v>17</v>
+      </c>
+      <c r="I1244" s="2">
+        <v>15</v>
+      </c>
+      <c r="J1244" s="2">
+        <v>0.63</v>
+      </c>
+      <c r="K1244" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:11" ht="18">
+      <c r="A1245" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1245" s="6">
+        <v>42186</v>
+      </c>
+      <c r="C1245" s="2">
+        <v>66</v>
+      </c>
+      <c r="D1245" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E1245" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1245" s="2">
+        <v>37</v>
+      </c>
+      <c r="G1245" s="2">
+        <v>63</v>
+      </c>
+      <c r="H1245" s="2">
+        <v>17</v>
+      </c>
+      <c r="I1245" s="2">
+        <v>16</v>
+      </c>
+      <c r="J1245" s="2">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="K1245" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:11" ht="18">
+      <c r="A1246" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1246" s="6">
+        <v>42217</v>
+      </c>
+      <c r="C1246" s="2">
+        <v>72</v>
+      </c>
+      <c r="D1246" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E1246" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1246" s="2">
+        <v>34</v>
+      </c>
+      <c r="G1246" s="2">
+        <v>65</v>
+      </c>
+      <c r="H1246" s="2">
+        <v>23</v>
+      </c>
+      <c r="I1246" s="2">
+        <v>18</v>
+      </c>
+      <c r="J1246" s="2">
+        <v>0.81299999999999994</v>
+      </c>
+      <c r="K1246" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:11" ht="18">
+      <c r="A1247" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1247" s="6">
+        <v>42248</v>
+      </c>
+      <c r="C1247" s="2">
+        <v>81</v>
+      </c>
+      <c r="D1247" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E1247" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1247" s="2">
+        <v>47</v>
+      </c>
+      <c r="G1247" s="2">
+        <v>87</v>
+      </c>
+      <c r="H1247" s="2">
+        <v>29</v>
+      </c>
+      <c r="I1247" s="2">
+        <v>17</v>
+      </c>
+      <c r="J1247" s="2">
+        <v>0.84299999999999997</v>
+      </c>
+      <c r="K1247" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:11" ht="18">
+      <c r="A1248" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1248" s="6">
+        <v>42278</v>
+      </c>
+      <c r="C1248" s="2">
+        <v>104</v>
+      </c>
+      <c r="D1248" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E1248" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1248" s="2">
+        <v>70</v>
+      </c>
+      <c r="G1248" s="2">
+        <v>117</v>
+      </c>
+      <c r="H1248" s="2">
+        <v>32</v>
+      </c>
+      <c r="I1248" s="2">
+        <v>21</v>
+      </c>
+      <c r="J1248" s="2">
+        <v>0.89400000000000002</v>
+      </c>
+      <c r="K1248" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:11" ht="18">
+      <c r="A1249" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1249" s="6">
+        <v>42309</v>
+      </c>
+      <c r="C1249" s="2">
+        <v>87</v>
+      </c>
+      <c r="D1249" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E1249" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1249" s="2">
+        <v>64</v>
+      </c>
+      <c r="G1249" s="2">
+        <v>93</v>
+      </c>
+      <c r="H1249" s="2">
+        <v>24</v>
+      </c>
+      <c r="I1249" s="2">
+        <v>17</v>
+      </c>
+      <c r="J1249" s="2">
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="K1249" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:11" ht="18">
+      <c r="A1250" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1250" s="6">
+        <v>42339</v>
+      </c>
+      <c r="C1250" s="2">
+        <v>147</v>
+      </c>
+      <c r="D1250" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E1250" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1250" s="2">
+        <v>111</v>
+      </c>
+      <c r="G1250" s="2">
+        <v>166</v>
+      </c>
+      <c r="H1250" s="2">
+        <v>47</v>
+      </c>
+      <c r="I1250" s="2">
+        <v>19</v>
+      </c>
+      <c r="J1250" s="2">
+        <v>1.135</v>
+      </c>
+      <c r="K1250" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:11" ht="18">
+      <c r="A1251" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1251" s="6">
+        <v>42370</v>
+      </c>
+      <c r="C1251" s="2">
+        <v>148</v>
+      </c>
+      <c r="D1251" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E1251" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1251" s="2">
+        <v>112</v>
+      </c>
+      <c r="G1251" s="2">
+        <v>164</v>
+      </c>
+      <c r="H1251" s="2">
+        <v>45</v>
+      </c>
+      <c r="I1251" s="2">
+        <v>17</v>
+      </c>
+      <c r="J1251" s="2">
+        <v>1.3420000000000001</v>
+      </c>
+      <c r="K1251" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:11" ht="18">
+      <c r="A1252" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1252" s="6">
+        <v>42401</v>
+      </c>
+      <c r="C1252" s="2">
+        <v>119</v>
+      </c>
+      <c r="D1252" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E1252" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1252" s="2">
+        <v>83</v>
+      </c>
+      <c r="G1252" s="2">
+        <v>135</v>
+      </c>
+      <c r="H1252" s="2">
+        <v>27</v>
+      </c>
+      <c r="I1252" s="2">
+        <v>26</v>
+      </c>
+      <c r="J1252" s="2">
+        <v>1.0069999999999999</v>
+      </c>
+      <c r="K1252" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:11" ht="18">
+      <c r="A1253" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1253" s="6">
+        <v>42430</v>
+      </c>
+      <c r="C1253" s="2">
+        <v>105</v>
+      </c>
+      <c r="D1253" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E1253" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1253" s="2">
+        <v>72</v>
+      </c>
+      <c r="G1253" s="2">
+        <v>126</v>
+      </c>
+      <c r="H1253" s="2">
+        <v>33</v>
+      </c>
+      <c r="I1253" s="2">
+        <v>18</v>
+      </c>
+      <c r="J1253" s="2">
+        <v>0.748</v>
+      </c>
+      <c r="K1253" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:11" ht="18">
+      <c r="A1254" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1254" s="6">
+        <v>42461</v>
+      </c>
+      <c r="C1254" s="2">
+        <v>77</v>
+      </c>
+      <c r="D1254" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E1254" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1254" s="2">
+        <v>39</v>
+      </c>
+      <c r="G1254" s="2">
+        <v>81</v>
+      </c>
+      <c r="H1254" s="2">
+        <v>26</v>
+      </c>
+      <c r="I1254" s="2">
+        <v>14</v>
+      </c>
+      <c r="J1254" s="2">
+        <v>0.76</v>
+      </c>
+      <c r="K1254" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:11" ht="18">
+      <c r="A1255" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1255" s="6">
+        <v>42491</v>
+      </c>
+      <c r="C1255" s="2">
+        <v>81</v>
+      </c>
+      <c r="D1255" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="E1255" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1255" s="2">
+        <v>39</v>
+      </c>
+      <c r="G1255" s="2">
+        <v>80</v>
+      </c>
+      <c r="H1255" s="2">
+        <v>19</v>
+      </c>
+      <c r="I1255" s="2">
+        <v>13</v>
+      </c>
+      <c r="J1255" s="2">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="K1255" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:11" ht="18">
+      <c r="A1256" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1256" s="6">
+        <v>42522</v>
+      </c>
+      <c r="C1256" s="2">
+        <v>62</v>
+      </c>
+      <c r="D1256" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E1256" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1256" s="2">
+        <v>31</v>
+      </c>
+      <c r="G1256" s="2">
+        <v>57</v>
+      </c>
+      <c r="H1256" s="2">
+        <v>16</v>
+      </c>
+      <c r="I1256" s="2">
+        <v>15</v>
+      </c>
+      <c r="J1256" s="2">
+        <v>0.62</v>
+      </c>
+      <c r="K1256" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:11" ht="18">
+      <c r="A1257" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1257" s="6">
+        <v>42552</v>
+      </c>
+      <c r="C1257" s="2">
+        <v>51</v>
+      </c>
+      <c r="D1257" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E1257" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1257" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1257" s="2">
+        <v>41</v>
+      </c>
+      <c r="H1257" s="2">
+        <v>12</v>
+      </c>
+      <c r="I1257" s="2">
+        <v>10</v>
+      </c>
+      <c r="J1257" s="2">
+        <v>0.503</v>
+      </c>
+      <c r="K1257" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:11" ht="18">
+      <c r="A1258" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1258" s="6">
+        <v>42583</v>
+      </c>
+      <c r="C1258" s="2">
+        <v>67</v>
+      </c>
+      <c r="D1258" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="E1258" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1258" s="2">
+        <v>37</v>
+      </c>
+      <c r="G1258" s="2">
+        <v>63</v>
+      </c>
+      <c r="H1258" s="2">
+        <v>17</v>
+      </c>
+      <c r="I1258" s="2">
+        <v>10</v>
+      </c>
+      <c r="J1258" s="2">
+        <v>0.56799999999999995</v>
+      </c>
+      <c r="K1258" s="2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:11" ht="18">
+      <c r="A1259" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1259" s="6">
+        <v>42614</v>
+      </c>
+      <c r="C1259" s="2">
+        <v>94</v>
+      </c>
+      <c r="D1259" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E1259" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1259" s="2">
+        <v>45</v>
+      </c>
+      <c r="G1259" s="2">
+        <v>77</v>
+      </c>
+      <c r="H1259" s="2">
+        <v>27</v>
+      </c>
+      <c r="I1259" s="2">
+        <v>14</v>
+      </c>
+      <c r="J1259" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="K1259" s="2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:11" ht="18">
+      <c r="A1260" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1260" s="6">
+        <v>42644</v>
+      </c>
+      <c r="C1260" s="2">
+        <v>59</v>
+      </c>
+      <c r="D1260" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E1260" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1260" s="2">
+        <v>39</v>
+      </c>
+      <c r="G1260" s="2">
+        <v>62</v>
+      </c>
+      <c r="H1260" s="2">
+        <v>31</v>
+      </c>
+      <c r="I1260" s="2">
+        <v>9</v>
+      </c>
+      <c r="J1260" s="2">
+        <v>0.66100000000000003</v>
+      </c>
+      <c r="K1260" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:11" ht="18">
+      <c r="A1261" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1261" s="6">
+        <v>42675</v>
+      </c>
+      <c r="C1261" s="2">
+        <v>96</v>
+      </c>
+      <c r="D1261" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E1261" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1261" s="2">
+        <v>72</v>
+      </c>
+      <c r="G1261" s="2">
+        <v>112</v>
+      </c>
+      <c r="H1261" s="2">
+        <v>36</v>
+      </c>
+      <c r="I1261" s="2">
+        <v>12</v>
+      </c>
+      <c r="J1261" s="2">
+        <v>0.88300000000000001</v>
+      </c>
+      <c r="K1261" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:11" ht="18">
+      <c r="A1262" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1262" s="6">
+        <v>42705</v>
+      </c>
+      <c r="C1262" s="2">
+        <v>131</v>
+      </c>
+      <c r="D1262" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E1262" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1262" s="2">
+        <v>100</v>
+      </c>
+      <c r="G1262" s="2">
+        <v>152</v>
+      </c>
+      <c r="H1262" s="2">
+        <v>46</v>
+      </c>
+      <c r="I1262" s="2">
+        <v>21</v>
+      </c>
+      <c r="J1262" s="2">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="K1262" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:11" ht="18">
+      <c r="A1263" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1263" s="6">
+        <v>42736</v>
+      </c>
+      <c r="C1263" s="2">
+        <v>99</v>
+      </c>
+      <c r="D1263" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E1263" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1263" s="2">
+        <v>73</v>
+      </c>
+      <c r="G1263" s="2">
+        <v>114</v>
+      </c>
+      <c r="H1263" s="2">
+        <v>44</v>
+      </c>
+      <c r="I1263" s="2">
+        <v>22</v>
+      </c>
+      <c r="J1263" s="2">
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="K1263" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:11" ht="18">
+      <c r="A1264" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1264" s="6">
+        <v>42767</v>
+      </c>
+      <c r="C1264" s="2">
+        <v>79</v>
+      </c>
+      <c r="D1264" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E1264" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1264" s="2">
+        <v>58</v>
+      </c>
+      <c r="G1264" s="2">
+        <v>89</v>
+      </c>
+      <c r="H1264" s="2">
+        <v>33</v>
+      </c>
+      <c r="I1264" s="2">
+        <v>17</v>
+      </c>
+      <c r="J1264" s="2">
+        <v>0.746</v>
+      </c>
+      <c r="K1264" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:11" ht="18">
+      <c r="A1265" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1265" s="6">
+        <v>42795</v>
+      </c>
+      <c r="C1265" s="2">
+        <v>75</v>
+      </c>
+      <c r="D1265" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E1265" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1265" s="2">
+        <v>52</v>
+      </c>
+      <c r="G1265" s="2">
+        <v>88</v>
+      </c>
+      <c r="H1265" s="2">
+        <v>37</v>
+      </c>
+      <c r="I1265" s="2">
+        <v>18</v>
+      </c>
+      <c r="J1265" s="2">
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="K1265" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:11" ht="18">
+      <c r="A1266" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1266" s="6">
+        <v>42826</v>
+      </c>
+      <c r="C1266" s="2">
+        <v>75</v>
+      </c>
+      <c r="D1266" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E1266" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1266" s="2">
+        <v>39</v>
+      </c>
+      <c r="G1266" s="2">
+        <v>66</v>
+      </c>
+      <c r="H1266" s="2">
+        <v>25</v>
+      </c>
+      <c r="I1266" s="2">
+        <v>13</v>
+      </c>
+      <c r="J1266" s="2">
+        <v>0.88700000000000001</v>
+      </c>
+      <c r="K1266" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:11" ht="18">
+      <c r="A1267" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1267" s="6">
+        <v>42856</v>
+      </c>
+      <c r="C1267" s="2">
+        <v>78</v>
+      </c>
+      <c r="D1267" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E1267" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1267" s="2">
+        <v>32</v>
+      </c>
+      <c r="G1267" s="2">
+        <v>51</v>
+      </c>
+      <c r="H1267" s="2">
+        <v>20</v>
+      </c>
+      <c r="I1267" s="2">
+        <v>9</v>
+      </c>
+      <c r="J1267" s="2">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="K1267" s="2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:11" ht="18">
+      <c r="A1268" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1268" s="6">
+        <v>42887</v>
+      </c>
+      <c r="C1268" s="2">
+        <v>73</v>
+      </c>
+      <c r="D1268" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1268" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1268" s="2">
+        <v>38</v>
+      </c>
+      <c r="G1268" s="2">
+        <v>56</v>
+      </c>
+      <c r="H1268" s="2">
+        <v>17</v>
+      </c>
+      <c r="I1268" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1268" s="2">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="K1268" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:11" ht="18">
+      <c r="A1269" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1269" s="6">
+        <v>42917</v>
+      </c>
+      <c r="C1269" s="2">
+        <v>57</v>
+      </c>
+      <c r="D1269" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E1269" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1269" s="2">
+        <v>28</v>
+      </c>
+      <c r="G1269" s="2">
+        <v>51</v>
+      </c>
+      <c r="H1269" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1269" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1269" s="2">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="K1269" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:11" ht="18">
+      <c r="A1270" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1270" s="6">
+        <v>42948</v>
+      </c>
+      <c r="C1270" s="2">
+        <v>66</v>
+      </c>
+      <c r="D1270" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E1270" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1270" s="2">
+        <v>30</v>
+      </c>
+      <c r="G1270" s="2">
+        <v>56</v>
+      </c>
+      <c r="H1270" s="2">
+        <v>15</v>
+      </c>
+      <c r="I1270" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1270" s="2">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="K1270" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:11" ht="18">
+      <c r="A1271" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1271" s="6">
+        <v>42979</v>
+      </c>
+      <c r="C1271" s="2">
+        <v>71</v>
+      </c>
+      <c r="D1271" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E1271" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1271" s="2">
+        <v>28</v>
+      </c>
+      <c r="G1271" s="2">
+        <v>59</v>
+      </c>
+      <c r="H1271" s="2">
+        <v>20</v>
+      </c>
+      <c r="I1271" s="2">
+        <v>9</v>
+      </c>
+      <c r="J1271" s="2">
+        <v>0.68</v>
+      </c>
+      <c r="K1271" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:11" ht="18">
+      <c r="A1272" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1272" s="6">
+        <v>43009</v>
+      </c>
+      <c r="C1272" s="2">
+        <v>68</v>
+      </c>
+      <c r="D1272" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E1272" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1272" s="2">
+        <v>43</v>
+      </c>
+      <c r="G1272" s="2">
+        <v>75</v>
+      </c>
+      <c r="H1272" s="2">
+        <v>28</v>
+      </c>
+      <c r="I1272" s="2">
+        <v>11</v>
+      </c>
+      <c r="J1272" s="2">
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="K1272" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:11" ht="18">
+      <c r="A1273" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1273" s="6">
+        <v>43040</v>
+      </c>
+      <c r="C1273" s="2">
+        <v>61</v>
+      </c>
+      <c r="D1273" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E1273" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1273" s="2">
+        <v>42</v>
+      </c>
+      <c r="G1273" s="2">
+        <v>75</v>
+      </c>
+      <c r="H1273" s="2">
+        <v>41</v>
+      </c>
+      <c r="I1273" s="2">
+        <v>13</v>
+      </c>
+      <c r="J1273" s="2">
+        <v>0.91300000000000003</v>
+      </c>
+      <c r="K1273" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:11" ht="18">
+      <c r="A1274" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1274" s="6">
+        <v>43070</v>
+      </c>
+      <c r="C1274" s="2">
+        <v>118</v>
+      </c>
+      <c r="D1274" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E1274" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1274" s="2">
+        <v>89</v>
+      </c>
+      <c r="G1274" s="2">
+        <v>135</v>
+      </c>
+      <c r="H1274" s="2">
+        <v>44</v>
+      </c>
+      <c r="I1274" s="2">
+        <v>14</v>
+      </c>
+      <c r="J1274" s="2">
+        <v>1.3480000000000001</v>
+      </c>
+      <c r="K1274" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:11" ht="18">
+      <c r="A1275" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1275" s="6">
+        <v>43101</v>
+      </c>
+      <c r="C1275" s="2">
+        <v>120</v>
+      </c>
+      <c r="D1275" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E1275" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1275" s="2">
+        <v>90</v>
+      </c>
+      <c r="G1275" s="2">
+        <v>134</v>
+      </c>
+      <c r="H1275" s="2">
+        <v>40</v>
+      </c>
+      <c r="I1275" s="2">
+        <v>10</v>
+      </c>
+      <c r="J1275" s="2">
+        <v>1.161</v>
+      </c>
+      <c r="K1275" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:11" ht="18">
+      <c r="A1276" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1276" s="6">
+        <v>43132</v>
+      </c>
+      <c r="C1276" s="2">
+        <v>83</v>
+      </c>
+      <c r="D1276" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E1276" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1276" s="2">
+        <v>60</v>
+      </c>
+      <c r="G1276" s="2">
+        <v>100</v>
+      </c>
+      <c r="H1276" s="2">
+        <v>31</v>
+      </c>
+      <c r="I1276" s="2">
+        <v>11</v>
+      </c>
+      <c r="J1276" s="2">
+        <v>1.032</v>
+      </c>
+      <c r="K1276" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:11" ht="18">
+      <c r="A1277" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1277" s="6">
+        <v>43160</v>
+      </c>
+      <c r="C1277" s="2">
+        <v>76</v>
+      </c>
+      <c r="D1277" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E1277" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1277" s="2">
+        <v>48</v>
+      </c>
+      <c r="G1277" s="2">
+        <v>76</v>
+      </c>
+      <c r="H1277" s="2">
+        <v>23</v>
+      </c>
+      <c r="I1277" s="2">
+        <v>10</v>
+      </c>
+      <c r="J1277" s="2">
+        <v>0.78700000000000003</v>
+      </c>
+      <c r="K1277" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:11" ht="18">
+      <c r="A1278" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1278" s="6">
+        <v>43191</v>
+      </c>
+      <c r="C1278" s="2">
+        <v>71</v>
+      </c>
+      <c r="D1278" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1278" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1278" s="2">
+        <v>36</v>
+      </c>
+      <c r="G1278" s="2">
+        <v>73</v>
+      </c>
+      <c r="H1278" s="2">
+        <v>19</v>
+      </c>
+      <c r="I1278" s="2">
+        <v>9</v>
+      </c>
+      <c r="J1278" s="2">
+        <v>0.69</v>
+      </c>
+      <c r="K1278" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:11" ht="18">
+      <c r="A1279" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1279" s="6">
+        <v>43221</v>
+      </c>
+      <c r="C1279" s="2">
+        <v>71</v>
+      </c>
+      <c r="D1279" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E1279" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1279" s="2">
+        <v>31</v>
+      </c>
+      <c r="G1279" s="2">
+        <v>65</v>
+      </c>
+      <c r="H1279" s="2">
+        <v>16</v>
+      </c>
+      <c r="I1279" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1279" s="2">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="K1279" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:11" ht="18">
+      <c r="A1280" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1280" s="6">
+        <v>43252</v>
+      </c>
+      <c r="C1280" s="2">
+        <v>89</v>
+      </c>
+      <c r="D1280" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E1280" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1280" s="2">
+        <v>28</v>
+      </c>
+      <c r="G1280" s="2">
+        <v>46</v>
+      </c>
+      <c r="H1280" s="2">
+        <v>14</v>
+      </c>
+      <c r="I1280" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1280" s="2">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="K1280" s="2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:11" ht="18">
+      <c r="A1281" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1281" s="6">
+        <v>43282</v>
+      </c>
+      <c r="C1281" s="2">
+        <v>60</v>
+      </c>
+      <c r="D1281" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="E1281" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1281" s="2">
+        <v>26</v>
+      </c>
+      <c r="G1281" s="2">
+        <v>43</v>
+      </c>
+      <c r="H1281" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1281" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1281" s="2">
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="K1281" s="2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:11" ht="18">
+      <c r="A1282" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1282" s="6">
+        <v>43313</v>
+      </c>
+      <c r="C1282" s="2">
+        <v>76</v>
+      </c>
+      <c r="D1282" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E1282" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1282" s="2">
+        <v>27</v>
+      </c>
+      <c r="G1282" s="2">
+        <v>45</v>
+      </c>
+      <c r="H1282" s="2">
+        <v>14</v>
+      </c>
+      <c r="I1282" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1282" s="2">
+        <v>0.51300000000000001</v>
+      </c>
+      <c r="K1282" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:11" ht="18">
+      <c r="A1283" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1283" s="6">
+        <v>43344</v>
+      </c>
+      <c r="C1283" s="2">
+        <v>76</v>
+      </c>
+      <c r="D1283" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E1283" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1283" s="2">
+        <v>29</v>
+      </c>
+      <c r="G1283" s="2">
+        <v>54</v>
+      </c>
+      <c r="H1283" s="2">
+        <v>21</v>
+      </c>
+      <c r="I1283" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1283" s="2">
+        <v>0.52</v>
+      </c>
+      <c r="K1283" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:11" ht="18">
+      <c r="A1284" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1284" s="6">
+        <v>43374</v>
+      </c>
+      <c r="C1284" s="2">
+        <v>86</v>
+      </c>
+      <c r="D1284" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="E1284" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1284" s="2">
+        <v>40</v>
+      </c>
+      <c r="G1284" s="2">
+        <v>71</v>
+      </c>
+      <c r="H1284" s="2">
+        <v>31</v>
+      </c>
+      <c r="I1284" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1284" s="2">
+        <v>0.57699999999999996</v>
+      </c>
+      <c r="K1284" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:11" ht="18">
+      <c r="A1285" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1285" s="6">
+        <v>43405</v>
+      </c>
+      <c r="C1285" s="2">
+        <v>78</v>
+      </c>
+      <c r="D1285" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E1285" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1285" s="2">
+        <v>57</v>
+      </c>
+      <c r="G1285" s="2">
+        <v>79</v>
+      </c>
+      <c r="H1285" s="2">
+        <v>37</v>
+      </c>
+      <c r="I1285" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1285" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="K1285" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:11" ht="18">
+      <c r="A1286" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1286" s="6">
+        <v>43435</v>
+      </c>
+      <c r="C1286" s="2">
+        <v>119</v>
+      </c>
+      <c r="D1286" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E1286" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1286" s="2">
+        <v>90</v>
+      </c>
+      <c r="G1286" s="2">
+        <v>134</v>
+      </c>
+      <c r="H1286" s="2">
+        <v>44</v>
+      </c>
+      <c r="I1286" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1286" s="2">
+        <v>1.0649999999999999</v>
+      </c>
+      <c r="K1286" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:11" ht="18">
+      <c r="A1287" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1287" s="6">
+        <v>43466</v>
+      </c>
+      <c r="C1287" s="2">
+        <v>140</v>
+      </c>
+      <c r="D1287" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E1287" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1287" s="2">
+        <v>106</v>
+      </c>
+      <c r="G1287" s="2">
+        <v>145</v>
+      </c>
+      <c r="H1287" s="2">
+        <v>39</v>
+      </c>
+      <c r="I1287" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1287" s="2">
+        <v>1.087</v>
+      </c>
+      <c r="K1287" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:11" ht="18">
+      <c r="A1288" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1288" s="6">
+        <v>43497</v>
+      </c>
+      <c r="C1288" s="2">
+        <v>115</v>
+      </c>
+      <c r="D1288" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E1288" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1288" s="2">
+        <v>87</v>
+      </c>
+      <c r="G1288" s="2">
+        <v>110</v>
+      </c>
+      <c r="H1288" s="2">
+        <v>23</v>
+      </c>
+      <c r="I1288" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1288" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="K1288" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:11" ht="18">
+      <c r="A1289" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1289" s="6">
+        <v>43525</v>
+      </c>
+      <c r="C1289" s="2">
+        <v>81</v>
+      </c>
+      <c r="D1289" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E1289" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1289" s="2">
+        <v>51</v>
+      </c>
+      <c r="G1289" s="2">
+        <v>89</v>
+      </c>
+      <c r="H1289" s="2">
+        <v>25</v>
+      </c>
+      <c r="I1289" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1289" s="2">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="K1289" s="2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:11" ht="18">
+      <c r="A1290" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1290" s="6">
+        <v>43556</v>
+      </c>
+      <c r="C1290" s="2">
+        <v>77</v>
+      </c>
+      <c r="D1290" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E1290" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1290" s="2">
+        <v>41</v>
+      </c>
+      <c r="G1290" s="2">
+        <v>69</v>
+      </c>
+      <c r="H1290" s="2">
+        <v>22</v>
+      </c>
+      <c r="I1290" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1290" s="2">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="K1290" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:11" ht="18">
+      <c r="A1291" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1291" s="6">
+        <v>43586</v>
+      </c>
+      <c r="C1291" s="2">
+        <v>85</v>
+      </c>
+      <c r="D1291" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E1291" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1291" s="2">
+        <v>31</v>
+      </c>
+      <c r="G1291" s="2">
+        <v>71</v>
+      </c>
+      <c r="H1291" s="2">
+        <v>15</v>
+      </c>
+      <c r="I1291" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1291" s="2">
+        <v>0.52600000000000002</v>
+      </c>
+      <c r="K1291" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:11" ht="18">
+      <c r="A1292" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1292" s="6">
+        <v>43617</v>
+      </c>
+      <c r="C1292" s="2">
+        <v>92</v>
+      </c>
+      <c r="D1292" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E1292" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1292" s="2">
+        <v>24</v>
+      </c>
+      <c r="G1292" s="2">
+        <v>45</v>
+      </c>
+      <c r="H1292" s="2">
+        <v>12</v>
+      </c>
+      <c r="I1292" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1292" s="2">
+        <v>0.54</v>
+      </c>
+      <c r="K1292" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:11" ht="18">
+      <c r="A1293" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1293" s="6">
+        <v>43647</v>
+      </c>
+      <c r="C1293" s="2">
+        <v>78</v>
+      </c>
+      <c r="D1293" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E1293" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1293" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1293" s="2">
+        <v>37</v>
+      </c>
+      <c r="H1293" s="2">
+        <v>12</v>
+      </c>
+      <c r="I1293" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1293" s="2">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="K1293" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:11" ht="18">
+      <c r="A1294" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1294" s="6">
+        <v>43678</v>
+      </c>
+      <c r="C1294" s="2">
+        <v>89</v>
+      </c>
+      <c r="D1294" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E1294" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1294" s="2">
+        <v>23</v>
+      </c>
+      <c r="G1294" s="2">
+        <v>42</v>
+      </c>
+      <c r="H1294" s="2">
+        <v>14</v>
+      </c>
+      <c r="I1294" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1294" s="2">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="K1294" s="2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:11" ht="18">
+      <c r="A1295" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1295" s="6">
+        <v>43709</v>
+      </c>
+      <c r="C1295" s="2">
+        <v>98</v>
+      </c>
+      <c r="D1295" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E1295" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1295" s="2">
+        <v>28</v>
+      </c>
+      <c r="G1295" s="2">
+        <v>53</v>
+      </c>
+      <c r="H1295" s="2">
+        <v>21</v>
+      </c>
+      <c r="I1295" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1295" s="2">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="K1295" s="2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:11" ht="18">
+      <c r="A1296" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1296" s="6">
+        <v>43739</v>
+      </c>
+      <c r="C1296" s="2">
+        <v>67</v>
+      </c>
+      <c r="D1296" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="E1296" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1296" s="2">
+        <v>33</v>
+      </c>
+      <c r="G1296" s="2">
+        <v>59</v>
+      </c>
+      <c r="H1296" s="2">
+        <v>27</v>
+      </c>
+      <c r="I1296" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1296" s="2">
+        <v>0.371</v>
+      </c>
+      <c r="K1296" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:11" ht="18">
+      <c r="A1297" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1297" s="6">
+        <v>43770</v>
+      </c>
+      <c r="C1297" s="2">
+        <v>82</v>
+      </c>
+      <c r="D1297" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E1297" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1297" s="2">
+        <v>54</v>
+      </c>
+      <c r="G1297" s="2">
+        <v>92</v>
+      </c>
+      <c r="H1297" s="2">
+        <v>35</v>
+      </c>
+      <c r="I1297" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1297" s="2">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="K1297" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:11" ht="18">
+      <c r="A1298" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1298" s="6">
+        <v>43800</v>
+      </c>
+      <c r="C1298" s="2">
+        <v>99</v>
+      </c>
+      <c r="D1298" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E1298" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1298" s="2">
+        <v>73</v>
+      </c>
+      <c r="G1298" s="2">
+        <v>106</v>
+      </c>
+      <c r="H1298" s="2">
+        <v>40</v>
+      </c>
+      <c r="I1298" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1298" s="2">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="K1298" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:11" ht="18">
+      <c r="A1299" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1299" s="6">
+        <v>43831</v>
+      </c>
+      <c r="C1299" s="2">
+        <v>114</v>
+      </c>
+      <c r="D1299" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E1299" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1299" s="2">
+        <v>85</v>
+      </c>
+      <c r="G1299" s="2">
+        <v>111</v>
+      </c>
+      <c r="H1299" s="2">
+        <v>32</v>
+      </c>
+      <c r="I1299" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1299" s="2">
+        <v>1.087</v>
+      </c>
+      <c r="K1299" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:11" ht="18">
+      <c r="A1300" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1300" s="6">
+        <v>43862</v>
+      </c>
+      <c r="C1300" s="2">
+        <v>72</v>
+      </c>
+      <c r="D1300" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E1300" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1300" s="2">
+        <v>50</v>
+      </c>
+      <c r="G1300" s="2">
+        <v>69</v>
+      </c>
+      <c r="H1300" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1300" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1300" s="2">
+        <v>0.78300000000000003</v>
+      </c>
+      <c r="K1300" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:11" ht="18">
+      <c r="A1301" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1301" s="6">
+        <v>43891</v>
+      </c>
+      <c r="C1301" s="2">
+        <v>70</v>
+      </c>
+      <c r="D1301" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="E1301" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1301" s="2">
+        <v>40</v>
+      </c>
+      <c r="G1301" s="2">
+        <v>74</v>
+      </c>
+      <c r="H1301" s="2">
+        <v>19</v>
+      </c>
+      <c r="I1301" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1301" s="2">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="K1301" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:11" ht="18">
+      <c r="A1302" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1302" s="6">
+        <v>43922</v>
+      </c>
+      <c r="C1302" s="2">
+        <v>84</v>
+      </c>
+      <c r="D1302" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E1302" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1302" s="2">
+        <v>36</v>
+      </c>
+      <c r="G1302" s="2">
+        <v>65</v>
+      </c>
+      <c r="H1302" s="2">
+        <v>21</v>
+      </c>
+      <c r="I1302" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1302" s="2">
+        <v>0.64700000000000002</v>
+      </c>
+      <c r="K1302" s="2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:11" ht="18">
+      <c r="A1303" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1303" s="6">
+        <v>43952</v>
+      </c>
+      <c r="C1303" s="2">
+        <v>83</v>
+      </c>
+      <c r="D1303" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E1303" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1303" s="2">
+        <v>28</v>
+      </c>
+      <c r="G1303" s="2">
+        <v>53</v>
+      </c>
+      <c r="H1303" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1303" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1303" s="2">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="K1303" s="2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:11" ht="18">
+      <c r="A1304" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1304" s="6">
+        <v>43983</v>
+      </c>
+      <c r="C1304" s="2">
+        <v>65</v>
+      </c>
+      <c r="D1304" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E1304" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1304" s="2">
+        <v>20</v>
+      </c>
+      <c r="G1304" s="2">
+        <v>34</v>
+      </c>
+      <c r="H1304" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1304" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1304" s="2">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="K1304" s="2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:11" ht="18">
+      <c r="A1305" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1305" s="6">
+        <v>44013</v>
+      </c>
+      <c r="C1305" s="2">
+        <v>55</v>
+      </c>
+      <c r="D1305" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E1305" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1305" s="2">
+        <v>21</v>
+      </c>
+      <c r="G1305" s="2">
+        <v>34</v>
+      </c>
+      <c r="H1305" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1305" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1305" s="2">
+        <v>0.503</v>
+      </c>
+      <c r="K1305" s="2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:11" ht="18">
+      <c r="A1306" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1306" s="6">
+        <v>44044</v>
+      </c>
+      <c r="C1306" s="2">
+        <v>61</v>
+      </c>
+      <c r="D1306" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E1306" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1306" s="2">
+        <v>18</v>
+      </c>
+      <c r="G1306" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1306" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1306" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1306" s="2">
+        <v>0.497</v>
+      </c>
+      <c r="K1306" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:11" ht="18">
+      <c r="A1307" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1307" s="6">
+        <v>44075</v>
+      </c>
+      <c r="C1307" s="2">
+        <v>81</v>
+      </c>
+      <c r="D1307" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E1307" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1307" s="2">
+        <v>27</v>
+      </c>
+      <c r="G1307" s="2">
+        <v>48</v>
+      </c>
+      <c r="H1307" s="2">
+        <v>15</v>
+      </c>
+      <c r="I1307" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1307" s="2">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="K1307" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:11" ht="18">
+      <c r="A1308" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1308" s="6">
+        <v>44105</v>
+      </c>
+      <c r="C1308" s="2">
+        <v>70</v>
+      </c>
+      <c r="D1308" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="E1308" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1308" s="2">
+        <v>42</v>
+      </c>
+      <c r="G1308" s="2">
+        <v>73</v>
+      </c>
+      <c r="H1308" s="2">
+        <v>28</v>
+      </c>
+      <c r="I1308" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1308" s="2">
+        <v>0.60599999999999998</v>
+      </c>
+      <c r="K1308" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:11" ht="18">
+      <c r="A1309" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1309" s="6">
+        <v>44136</v>
+      </c>
+      <c r="C1309" s="2">
+        <v>71</v>
+      </c>
+      <c r="D1309" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E1309" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1309" s="2">
+        <v>45</v>
+      </c>
+      <c r="G1309" s="2">
+        <v>74</v>
+      </c>
+      <c r="H1309" s="2">
+        <v>32</v>
+      </c>
+      <c r="I1309" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1309" s="2">
+        <v>0.70299999999999996</v>
+      </c>
+      <c r="K1309" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:11" ht="18">
+      <c r="A1310" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1310" s="6">
+        <v>44166</v>
+      </c>
+      <c r="C1310" s="2">
+        <v>96</v>
+      </c>
+      <c r="D1310" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1310" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1310" s="2">
+        <v>70</v>
+      </c>
+      <c r="G1310" s="2">
+        <v>101</v>
+      </c>
+      <c r="H1310" s="2">
+        <v>36</v>
+      </c>
+      <c r="I1310" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1310" s="2">
+        <v>0.91900000000000004</v>
+      </c>
+      <c r="K1310" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:11" ht="18">
+      <c r="A1311" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1311" s="6">
+        <v>44197</v>
+      </c>
+      <c r="C1311" s="2">
+        <v>118</v>
+      </c>
+      <c r="D1311" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E1311" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1311" s="2">
+        <v>72</v>
+      </c>
+      <c r="G1311" s="2">
+        <v>107</v>
+      </c>
+      <c r="H1311" s="2">
+        <v>36</v>
+      </c>
+      <c r="I1311" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1311" s="2">
+        <v>0.98099999999999998</v>
+      </c>
+      <c r="K1311" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:11" ht="18">
+      <c r="A1312" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1312" s="6">
+        <v>44228</v>
+      </c>
+      <c r="C1312" s="2">
+        <v>78</v>
+      </c>
+      <c r="D1312" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E1312" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1312" s="2">
+        <v>54</v>
+      </c>
+      <c r="G1312" s="2">
+        <v>89</v>
+      </c>
+      <c r="H1312" s="2">
+        <v>20</v>
+      </c>
+      <c r="I1312" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1312" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="K1312" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:11" ht="18">
+      <c r="A1313" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1313" s="6">
+        <v>44256</v>
+      </c>
+      <c r="C1313" s="2">
+        <v>89</v>
+      </c>
+      <c r="D1313" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E1313" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1313" s="2">
+        <v>30</v>
+      </c>
+      <c r="G1313" s="2">
+        <v>53</v>
+      </c>
+      <c r="H1313" s="2">
+        <v>22</v>
+      </c>
+      <c r="I1313" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1313" s="2">
+        <v>0.66100000000000003</v>
+      </c>
+      <c r="K1313" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:11" ht="18">
+      <c r="A1314" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1314" s="6">
+        <v>44287</v>
+      </c>
+      <c r="C1314" s="2">
+        <v>72</v>
+      </c>
+      <c r="D1314" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E1314" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1314" s="2">
+        <v>33</v>
+      </c>
+      <c r="G1314" s="2">
+        <v>55</v>
+      </c>
+      <c r="H1314" s="2">
+        <v>20</v>
+      </c>
+      <c r="I1314" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1314" s="2">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="K1314" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:11" ht="18">
+      <c r="A1315" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1315" s="6">
+        <v>44317</v>
+      </c>
+      <c r="C1315" s="2">
+        <v>65</v>
+      </c>
+      <c r="D1315" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E1315" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1315" s="2">
+        <v>27</v>
+      </c>
+      <c r="G1315" s="2">
+        <v>45</v>
+      </c>
+      <c r="H1315" s="2">
+        <v>12</v>
+      </c>
+      <c r="I1315" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1315" s="2">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="K1315" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:11" ht="18">
+      <c r="A1316" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1316" s="6">
+        <v>44348</v>
+      </c>
+      <c r="C1316" s="2">
+        <v>79</v>
+      </c>
+      <c r="D1316" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="E1316" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1316" s="2">
+        <v>22</v>
+      </c>
+      <c r="G1316" s="2">
+        <v>38</v>
+      </c>
+      <c r="H1316" s="2">
+        <v>11</v>
+      </c>
+      <c r="I1316" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1316" s="2">
+        <v>0.503</v>
+      </c>
+      <c r="K1316" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:11" ht="18">
+      <c r="A1317" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1317" s="6">
+        <v>44378</v>
+      </c>
+      <c r="C1317" s="2">
+        <v>49</v>
+      </c>
+      <c r="D1317" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E1317" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1317" s="2">
+        <v>15</v>
+      </c>
+      <c r="G1317" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1317" s="2">
+        <v>8</v>
+      </c>
+      <c r="I1317" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1317" s="2">
+        <v>0.41</v>
+      </c>
+      <c r="K1317" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:11" ht="18">
+      <c r="A1318" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1318" s="6">
+        <v>44409</v>
+      </c>
+      <c r="C1318" s="2">
+        <v>55</v>
+      </c>
+      <c r="D1318" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1318" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1318" s="2">
+        <v>19</v>
+      </c>
+      <c r="G1318" s="2">
+        <v>30</v>
+      </c>
+      <c r="H1318" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1318" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1318" s="2">
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="K1318" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:11" ht="18">
+      <c r="A1319" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1319" s="6">
+        <v>44440</v>
+      </c>
+      <c r="C1319" s="2">
+        <v>65</v>
+      </c>
+      <c r="D1319" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E1319" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1319" s="2">
+        <v>22</v>
+      </c>
+      <c r="G1319" s="2">
+        <v>37</v>
+      </c>
+      <c r="H1319" s="2">
+        <v>14</v>
+      </c>
+      <c r="I1319" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1319" s="2">
+        <v>0.48</v>
+      </c>
+      <c r="K1319" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:11" ht="18">
+      <c r="A1320" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1320" s="6">
+        <v>44470</v>
+      </c>
+      <c r="C1320" s="2">
+        <v>65</v>
+      </c>
+      <c r="D1320" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E1320" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1320" s="2">
+        <v>36</v>
+      </c>
+      <c r="G1320" s="2">
+        <v>57</v>
+      </c>
+      <c r="H1320" s="2">
+        <v>25</v>
+      </c>
+      <c r="I1320" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1320" s="2">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="K1320" s="2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:11" ht="18">
+      <c r="A1321" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1321" s="6">
+        <v>44501</v>
+      </c>
+      <c r="C1321" s="2">
+        <v>80</v>
+      </c>
+      <c r="D1321" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E1321" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1321" s="2">
+        <v>53</v>
+      </c>
+      <c r="G1321" s="2">
+        <v>83</v>
+      </c>
+      <c r="H1321" s="2">
+        <v>34</v>
+      </c>
+      <c r="I1321" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1321" s="2">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="K1321" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:11" ht="18">
+      <c r="A1322" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1322" s="6">
+        <v>44531</v>
+      </c>
+      <c r="C1322" s="2">
+        <v>87</v>
+      </c>
+      <c r="D1322" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1322" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1322" s="2">
+        <v>62</v>
+      </c>
+      <c r="G1322" s="2">
+        <v>90</v>
+      </c>
+      <c r="H1322" s="2">
+        <v>36</v>
+      </c>
+      <c r="I1322" s="2">
+        <v>9</v>
+      </c>
+      <c r="J1322" s="2">
+        <v>0.64200000000000002</v>
+      </c>
+      <c r="K1322" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:11" ht="18">
+      <c r="A1323" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1323" s="6">
+        <v>44562</v>
+      </c>
+      <c r="C1323" s="2">
+        <v>138</v>
+      </c>
+      <c r="D1323" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E1323" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1323" s="2">
+        <v>104</v>
+      </c>
+      <c r="G1323" s="2">
+        <v>118</v>
+      </c>
+      <c r="H1323" s="2">
+        <v>31</v>
+      </c>
+      <c r="I1323" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1323" s="2">
+        <v>0.89400000000000002</v>
+      </c>
+      <c r="K1323" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:11" ht="18">
+      <c r="A1324" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1324" s="6">
+        <v>44593</v>
+      </c>
+      <c r="C1324" s="2">
+        <v>79</v>
+      </c>
+      <c r="D1324" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E1324" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1324" s="2">
+        <v>57</v>
+      </c>
+      <c r="G1324" s="2">
+        <v>75</v>
+      </c>
+      <c r="H1324" s="2">
+        <v>20</v>
+      </c>
+      <c r="I1324" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1324" s="2">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="K1324" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:11" ht="18">
+      <c r="A1325" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1325" s="6">
+        <v>44621</v>
+      </c>
+      <c r="C1325" s="2">
+        <v>75</v>
+      </c>
+      <c r="D1325" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E1325" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1325" s="2">
+        <v>25</v>
+      </c>
+      <c r="G1325" s="2">
+        <v>41</v>
+      </c>
+      <c r="H1325" s="2">
+        <v>20</v>
+      </c>
+      <c r="I1325" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1325" s="2">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="K1325" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:11" ht="18">
+      <c r="A1326" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1326" s="6">
+        <v>44652</v>
+      </c>
+      <c r="C1326" s="2">
+        <v>78</v>
+      </c>
+      <c r="D1326" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E1326" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1326" s="2">
+        <v>29</v>
+      </c>
+      <c r="G1326" s="2">
+        <v>52</v>
+      </c>
+      <c r="H1326" s="2">
+        <v>16</v>
+      </c>
+      <c r="I1326" s="2">
+        <v>9</v>
+      </c>
+      <c r="J1326" s="2">
+        <v>0.47</v>
+      </c>
+      <c r="K1326" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:11" ht="18">
+      <c r="A1327" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1327" s="6">
+        <v>44682</v>
+      </c>
+      <c r="C1327" s="2">
+        <v>78</v>
+      </c>
+      <c r="D1327" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E1327" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1327" s="2">
+        <v>26</v>
+      </c>
+      <c r="G1327" s="2">
+        <v>46</v>
+      </c>
+      <c r="H1327" s="2">
+        <v>15</v>
+      </c>
+      <c r="I1327" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1327" s="2">
+        <v>0.51900000000000002</v>
+      </c>
+      <c r="K1327" s="2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:11" ht="18">
+      <c r="A1328" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1328" s="6">
+        <v>44713</v>
+      </c>
+      <c r="C1328" s="2">
+        <v>79</v>
+      </c>
+      <c r="D1328" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E1328" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1328" s="2">
+        <v>18</v>
+      </c>
+      <c r="G1328" s="2">
+        <v>31</v>
+      </c>
+      <c r="H1328" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1328" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1328" s="2">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="K1328" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:11" ht="18">
+      <c r="A1329" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1329" s="6">
+        <v>44743</v>
+      </c>
+      <c r="C1329" s="2">
+        <v>60</v>
+      </c>
+      <c r="D1329" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E1329" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1329" s="2">
+        <v>15</v>
+      </c>
+      <c r="G1329" s="2">
+        <v>24</v>
+      </c>
+      <c r="H1329" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1329" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1329" s="2">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="K1329" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:11" ht="18">
+      <c r="A1330" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1330" s="6">
+        <v>44774</v>
+      </c>
+      <c r="C1330" s="2">
+        <v>62</v>
+      </c>
+      <c r="D1330" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E1330" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1330" s="2">
+        <v>17</v>
+      </c>
+      <c r="G1330" s="2">
+        <v>31</v>
+      </c>
+      <c r="H1330" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1330" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1330" s="2">
+        <v>0.626</v>
+      </c>
+      <c r="K1330" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:11" ht="18">
+      <c r="A1331" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1331" s="6">
+        <v>44805</v>
+      </c>
+      <c r="C1331" s="2">
+        <v>87</v>
+      </c>
+      <c r="D1331" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1331" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1331" s="2">
+        <v>26</v>
+      </c>
+      <c r="G1331" s="2">
+        <v>57</v>
+      </c>
+      <c r="H1331" s="2">
+        <v>19</v>
+      </c>
+      <c r="I1331" s="2">
+        <v>9</v>
+      </c>
+      <c r="J1331" s="2">
+        <v>0.79300000000000004</v>
+      </c>
+      <c r="K1331" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:11" ht="18">
+      <c r="A1332" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1332" s="6">
+        <v>44835</v>
+      </c>
+      <c r="C1332" s="2">
+        <v>68</v>
+      </c>
+      <c r="D1332" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="E1332" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1332" s="2">
+        <v>34</v>
+      </c>
+      <c r="G1332" s="2">
+        <v>59</v>
+      </c>
+      <c r="H1332" s="2">
+        <v>24</v>
+      </c>
+      <c r="I1332" s="2">
+        <v>9</v>
+      </c>
+      <c r="J1332" s="2">
+        <v>0.68700000000000006</v>
+      </c>
+      <c r="K1332" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:11" ht="18">
+      <c r="A1333" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1333" s="6">
+        <v>44866</v>
+      </c>
+      <c r="C1333" s="2">
+        <v>69</v>
+      </c>
+      <c r="D1333" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E1333" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1333" s="2">
+        <v>47</v>
+      </c>
+      <c r="G1333" s="2">
+        <v>70</v>
+      </c>
+      <c r="H1333" s="2">
+        <v>25</v>
+      </c>
+      <c r="I1333" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1333" s="2">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="K1333" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:11" ht="18">
+      <c r="A1334" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1334" s="6">
+        <v>44896</v>
+      </c>
+      <c r="C1334" s="2">
+        <v>97</v>
+      </c>
+      <c r="D1334" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E1334" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1334" s="2">
+        <v>70</v>
+      </c>
+      <c r="G1334" s="2">
+        <v>102</v>
+      </c>
+      <c r="H1334" s="2">
+        <v>33</v>
+      </c>
+      <c r="I1334" s="2">
+        <v>9</v>
+      </c>
+      <c r="J1334" s="2">
+        <v>0.78400000000000003</v>
+      </c>
+      <c r="K1334" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:11" ht="18">
+      <c r="A1335" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1335" s="6">
+        <v>44927</v>
+      </c>
+      <c r="C1335" s="2">
+        <v>132</v>
+      </c>
+      <c r="D1335" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="E1335" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1335" s="2">
+        <v>100</v>
+      </c>
+      <c r="G1335" s="2">
+        <v>135</v>
+      </c>
+      <c r="H1335" s="2">
+        <v>28</v>
+      </c>
+      <c r="I1335" s="2">
+        <v>10</v>
+      </c>
+      <c r="J1335" s="2">
+        <v>1.032</v>
+      </c>
+      <c r="K1335" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:11" ht="18">
+      <c r="A1336" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1336" s="6">
+        <v>44958</v>
+      </c>
+      <c r="C1336" s="2">
+        <v>90</v>
+      </c>
+      <c r="D1336" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E1336" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1336" s="2">
+        <v>66</v>
+      </c>
+      <c r="G1336" s="2">
+        <v>90</v>
+      </c>
+      <c r="H1336" s="2">
+        <v>28</v>
+      </c>
+      <c r="I1336" s="2">
+        <v>9</v>
+      </c>
+      <c r="J1336" s="2">
+        <v>0.73599999999999999</v>
+      </c>
+      <c r="K1336" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:11" ht="18">
+      <c r="A1337" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1337" s="6">
+        <v>44986</v>
+      </c>
+      <c r="C1337" s="2">
+        <v>104</v>
+      </c>
+      <c r="D1337" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E1337" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1337" s="2">
+        <v>54</v>
+      </c>
+      <c r="G1337" s="2">
+        <v>122</v>
+      </c>
+      <c r="H1337" s="2">
+        <v>22</v>
+      </c>
+      <c r="I1337" s="2">
+        <v>10</v>
+      </c>
+      <c r="J1337" s="2">
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="K1337" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:11" ht="18">
+      <c r="A1338" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1338" s="6">
+        <v>45017</v>
+      </c>
+      <c r="C1338" s="2">
+        <v>99</v>
+      </c>
+      <c r="D1338" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E1338" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1338" s="2">
+        <v>43</v>
+      </c>
+      <c r="G1338" s="2">
+        <v>110</v>
+      </c>
+      <c r="H1338" s="2">
+        <v>17</v>
+      </c>
+      <c r="I1338" s="2">
+        <v>9</v>
+      </c>
+      <c r="J1338" s="2">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="K1338" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:11" ht="18">
+      <c r="A1339" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1339" s="6">
+        <v>45047</v>
+      </c>
+      <c r="C1339" s="2">
+        <v>68</v>
+      </c>
+      <c r="D1339" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E1339" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1339" s="2">
+        <v>27</v>
+      </c>
+      <c r="G1339" s="2">
+        <v>47</v>
+      </c>
+      <c r="H1339" s="2">
+        <v>14</v>
+      </c>
+      <c r="I1339" s="2">
+        <v>7</v>
+      </c>
+      <c r="J1339" s="2">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="K1339" s="2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:11" ht="18">
+      <c r="A1340" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1340" s="6">
+        <v>45078</v>
+      </c>
+      <c r="C1340" s="2">
+        <v>80</v>
+      </c>
+      <c r="D1340" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E1340" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1340" s="2">
+        <v>20</v>
+      </c>
+      <c r="G1340" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1340" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1340" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1340" s="2">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="K1340" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:11" ht="18">
+      <c r="A1341" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1341" s="6">
+        <v>45108</v>
+      </c>
+      <c r="C1341" s="2">
+        <v>56</v>
+      </c>
+      <c r="D1341" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E1341" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1341" s="2">
+        <v>15</v>
+      </c>
+      <c r="G1341" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1341" s="2">
+        <v>8</v>
+      </c>
+      <c r="I1341" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1341" s="2">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="K1341" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:11" ht="18">
+      <c r="A1342" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1342" s="6">
+        <v>45139</v>
+      </c>
+      <c r="C1342" s="2">
+        <v>77</v>
+      </c>
+      <c r="D1342" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E1342" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1342" s="2">
+        <v>20</v>
+      </c>
+      <c r="G1342" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1342" s="2">
+        <v>10</v>
+      </c>
+      <c r="I1342" s="2">
+        <v>2</v>
+      </c>
+      <c r="J1342" s="2">
+        <v>0.65800000000000003</v>
+      </c>
+      <c r="K1342" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:11" ht="18">
+      <c r="A1343" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1343" s="6">
+        <v>45170</v>
+      </c>
+      <c r="C1343" s="2">
+        <v>58</v>
+      </c>
+      <c r="D1343" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E1343" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1343" s="2">
+        <v>17</v>
+      </c>
+      <c r="G1343" s="2">
+        <v>34</v>
+      </c>
+      <c r="H1343" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1343" s="2">
+        <v>3</v>
+      </c>
+      <c r="J1343" s="2">
+        <v>0.75700000000000001</v>
+      </c>
+      <c r="K1343" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:11" ht="18">
+      <c r="A1344" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1344" s="6">
+        <v>45200</v>
+      </c>
+      <c r="C1344" s="2">
+        <v>72</v>
+      </c>
+      <c r="D1344" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E1344" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1344" s="2">
+        <v>32</v>
+      </c>
+      <c r="G1344" s="2">
+        <v>54</v>
+      </c>
+      <c r="H1344" s="2">
+        <v>19</v>
+      </c>
+      <c r="I1344" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1344" s="2">
+        <v>0.74199999999999999</v>
+      </c>
+      <c r="K1344" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:11" ht="18">
+      <c r="A1345" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1345" s="6">
+        <v>45231</v>
+      </c>
+      <c r="C1345" s="2">
+        <v>69</v>
+      </c>
+      <c r="D1345" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E1345" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1345" s="2">
+        <v>40</v>
+      </c>
+      <c r="G1345" s="2">
+        <v>71</v>
+      </c>
+      <c r="H1345" s="2">
+        <v>25</v>
+      </c>
+      <c r="I1345" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1345" s="2">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="K1345" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:11" ht="18">
+      <c r="A1346" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1346" s="6">
+        <v>45261</v>
+      </c>
+      <c r="C1346" s="2">
+        <v>85</v>
+      </c>
+      <c r="D1346" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E1346" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1346" s="2">
+        <v>61</v>
+      </c>
+      <c r="G1346" s="2">
+        <v>82</v>
+      </c>
+      <c r="H1346" s="2">
+        <v>29</v>
+      </c>
+      <c r="I1346" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1346" s="2">
+        <v>0.76100000000000001</v>
+      </c>
+      <c r="K1346" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:11" ht="18">
+      <c r="A1347" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1347" s="6">
+        <v>45292</v>
+      </c>
+      <c r="C1347" s="2">
+        <v>102</v>
+      </c>
+      <c r="D1347" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E1347" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1347" s="2">
+        <v>76</v>
+      </c>
+      <c r="G1347" s="2">
+        <v>92</v>
+      </c>
+      <c r="H1347" s="2">
+        <v>32</v>
+      </c>
+      <c r="I1347" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1347" s="2">
+        <v>0.83899999999999997</v>
+      </c>
+      <c r="K1347" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:11" ht="18">
+      <c r="A1348" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1348" s="6">
+        <v>45323</v>
+      </c>
+      <c r="C1348" s="2">
+        <v>85</v>
+      </c>
+      <c r="D1348" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E1348" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1348" s="2">
+        <v>61</v>
+      </c>
+      <c r="G1348" s="2">
+        <v>79</v>
+      </c>
+      <c r="H1348" s="2">
+        <v>17</v>
+      </c>
+      <c r="I1348" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1348" s="2">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="K1348" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:11" ht="18">
+      <c r="A1349" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1349" s="6">
+        <v>45352</v>
+      </c>
+      <c r="C1349" s="2">
+        <v>82</v>
+      </c>
+      <c r="D1349" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1349" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1349" s="2">
+        <v>48</v>
+      </c>
+      <c r="G1349" s="2">
+        <v>86</v>
+      </c>
+      <c r="H1349" s="2">
+        <v>19</v>
+      </c>
+      <c r="I1349" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1349" s="2">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="K1349" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:11" ht="18">
+      <c r="A1350" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1350" s="6">
+        <v>45383</v>
+      </c>
+      <c r="C1350" s="2">
+        <v>70</v>
+      </c>
+      <c r="D1350" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E1350" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1350" s="2">
+        <v>32</v>
+      </c>
+      <c r="G1350" s="2">
+        <v>61</v>
+      </c>
+      <c r="H1350" s="2">
+        <v>16</v>
+      </c>
+      <c r="I1350" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1350" s="2">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="K1350" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:11" ht="18">
+      <c r="A1351" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1351" s="6">
+        <v>45413</v>
+      </c>
+      <c r="C1351" s="2">
+        <v>98</v>
+      </c>
+      <c r="D1351" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E1351" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1351" s="2">
+        <v>28</v>
+      </c>
+      <c r="G1351" s="2">
+        <v>65</v>
+      </c>
+      <c r="H1351" s="2">
+        <v>12</v>
+      </c>
+      <c r="I1351" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1351" s="2">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="K1351" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:11" ht="18">
+      <c r="A1352" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1352" s="6">
+        <v>45444</v>
+      </c>
+      <c r="C1352" s="2">
+        <v>86</v>
+      </c>
+      <c r="D1352" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E1352" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1352" s="2">
+        <v>20</v>
+      </c>
+      <c r="G1352" s="2">
+        <v>41</v>
+      </c>
+      <c r="H1352" s="2">
+        <v>8</v>
+      </c>
+      <c r="I1352" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1352" s="2">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="K1352" s="2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:11" ht="18">
+      <c r="A1353" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1353" s="6">
+        <v>45474</v>
+      </c>
+      <c r="C1353" s="2">
+        <v>49</v>
+      </c>
+      <c r="D1353" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E1353" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1353" s="2">
+        <v>12</v>
+      </c>
+      <c r="G1353" s="2">
+        <v>25</v>
+      </c>
+      <c r="H1353" s="2">
+        <v>5</v>
+      </c>
+      <c r="I1353" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1353" s="2">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="K1353" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:11" ht="18">
+      <c r="A1354" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1354" s="6">
+        <v>45505</v>
+      </c>
+      <c r="C1354" s="2">
+        <v>64</v>
+      </c>
+      <c r="D1354" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E1354" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1354" s="2">
+        <v>15</v>
+      </c>
+      <c r="G1354" s="2">
+        <v>30</v>
+      </c>
+      <c r="H1354" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1354" s="2">
+        <v>2</v>
+      </c>
+      <c r="J1354" s="2">
+        <v>0.59</v>
+      </c>
+      <c r="K1354" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:11" ht="18">
+      <c r="A1355" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1355" s="6">
+        <v>45536</v>
+      </c>
+      <c r="C1355" s="2">
+        <v>71</v>
+      </c>
+      <c r="D1355" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E1355" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1355" s="2">
+        <v>23</v>
+      </c>
+      <c r="G1355" s="2">
+        <v>45</v>
+      </c>
+      <c r="H1355" s="2">
+        <v>14</v>
+      </c>
+      <c r="I1355" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1355" s="2">
+        <v>0.54300000000000004</v>
+      </c>
+      <c r="K1355" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:11" ht="18">
+      <c r="A1356" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1356" s="6">
+        <v>45566</v>
+      </c>
+      <c r="C1356" s="2">
+        <v>74</v>
+      </c>
+      <c r="D1356" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E1356" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1356" s="2">
+        <v>37</v>
+      </c>
+      <c r="G1356" s="2">
+        <v>60</v>
+      </c>
+      <c r="H1356" s="2">
+        <v>20</v>
+      </c>
+      <c r="I1356" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1356" s="2">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="K1356" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:11" ht="18">
+      <c r="A1357" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1357" s="6">
+        <v>45597</v>
+      </c>
+      <c r="C1357" s="2">
+        <v>66</v>
+      </c>
+      <c r="D1357" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E1357" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1357" s="2">
+        <v>41</v>
+      </c>
+      <c r="G1357" s="2">
+        <v>69</v>
+      </c>
+      <c r="H1357" s="2">
+        <v>22</v>
+      </c>
+      <c r="I1357" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1357" s="2">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="K1357" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:11" ht="18">
+      <c r="A1358" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1358" s="6">
+        <v>45627</v>
+      </c>
+      <c r="C1358" s="2">
+        <v>82</v>
+      </c>
+      <c r="D1358" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="E1358" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1358" s="2">
+        <v>59</v>
+      </c>
+      <c r="G1358" s="2">
+        <v>81</v>
+      </c>
+      <c r="H1358" s="2">
+        <v>29</v>
+      </c>
+      <c r="I1358" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1358" s="2">
+        <v>0.55200000000000005</v>
+      </c>
+      <c r="K1358" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:11" ht="18">
+      <c r="A1359" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1359" s="6">
+        <v>45658</v>
+      </c>
+      <c r="C1359" s="2">
+        <v>98</v>
+      </c>
+      <c r="D1359" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E1359" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1359" s="2">
+        <v>71</v>
+      </c>
+      <c r="G1359" s="2">
+        <v>98</v>
+      </c>
+      <c r="H1359" s="2">
+        <v>28</v>
+      </c>
+      <c r="I1359" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1359" s="2">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="K1359" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:11" ht="18">
+      <c r="A1360" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1360" s="6">
+        <v>45689</v>
+      </c>
+      <c r="C1360" s="2">
+        <v>83</v>
+      </c>
+      <c r="D1360" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="E1360" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1360" s="2">
+        <v>58</v>
+      </c>
+      <c r="G1360" s="2">
+        <v>83</v>
+      </c>
+      <c r="H1360" s="2">
+        <v>19</v>
+      </c>
+      <c r="I1360" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1360" s="2">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="K1360" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:11" ht="18">
+      <c r="A1361" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1361" s="6">
+        <v>45717</v>
+      </c>
+      <c r="C1361" s="2">
+        <v>76</v>
+      </c>
+      <c r="D1361" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="E1361" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1361" s="2">
+        <v>42</v>
+      </c>
+      <c r="G1361" s="2">
+        <v>64</v>
+      </c>
+      <c r="H1361" s="2">
+        <v>16</v>
+      </c>
+      <c r="I1361" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1361" s="2">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="K1361" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:11" ht="18">
+      <c r="A1362" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1362" s="6">
+        <v>45748</v>
+      </c>
+      <c r="C1362" s="2">
+        <v>91</v>
+      </c>
+      <c r="D1362" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="E1362" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1362" s="2">
+        <v>34</v>
+      </c>
+      <c r="G1362" s="2">
+        <v>77</v>
+      </c>
+      <c r="H1362" s="2">
+        <v>13</v>
+      </c>
+      <c r="I1362" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1362" s="2">
+        <v>0.47</v>
+      </c>
+      <c r="K1362" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:11" ht="18">
+      <c r="A1363" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1363" s="6">
+        <v>45778</v>
+      </c>
+      <c r="C1363" s="2">
+        <v>90</v>
+      </c>
+      <c r="D1363" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1363" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1363" s="2">
+        <v>34</v>
+      </c>
+      <c r="G1363" s="2">
+        <v>65</v>
+      </c>
+      <c r="H1363" s="2">
+        <v>11</v>
+      </c>
+      <c r="I1363" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1363" s="2">
+        <v>0.371</v>
+      </c>
+      <c r="K1363" s="2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:11" ht="18">
+      <c r="A1364" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1364" s="6">
+        <v>45809</v>
+      </c>
+      <c r="C1364" s="2">
+        <v>67</v>
+      </c>
+      <c r="D1364" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="E1364" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1364" s="2">
+        <v>17</v>
+      </c>
+      <c r="G1364" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1364" s="2">
+        <v>9</v>
+      </c>
+      <c r="I1364" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1364" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="K1364" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:11" ht="18">
+      <c r="A1365" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1365" s="6">
+        <v>45839</v>
+      </c>
+      <c r="C1365" s="2">
+        <v>59</v>
+      </c>
+      <c r="D1365" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E1365" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1365" s="2">
+        <v>14</v>
+      </c>
+      <c r="G1365" s="2">
+        <v>24</v>
+      </c>
+      <c r="H1365" s="2">
+        <v>8</v>
+      </c>
+      <c r="I1365" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1365" s="2">
+        <v>0.435</v>
+      </c>
+      <c r="K1365" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:11" ht="18">
+      <c r="A1366" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1366" s="6">
+        <v>45870</v>
+      </c>
+      <c r="C1366" s="2">
+        <v>55</v>
+      </c>
+      <c r="D1366" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E1366" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1366" s="2">
+        <v>13</v>
+      </c>
+      <c r="G1366" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1366" s="2">
+        <v>8</v>
+      </c>
+      <c r="I1366" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1366" s="2">
+        <v>0.497</v>
+      </c>
+      <c r="K1366" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:11" ht="18">
+      <c r="A1367" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1367" s="6">
+        <v>45901</v>
+      </c>
+      <c r="C1367" s="2">
+        <v>44</v>
+      </c>
+      <c r="D1367" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E1367" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1367" s="2">
+        <v>12</v>
+      </c>
+      <c r="G1367" s="2">
+        <v>24</v>
+      </c>
+      <c r="H1367" s="2">
+        <v>12</v>
+      </c>
+      <c r="I1367" s="2">
+        <v>4</v>
+      </c>
+      <c r="J1367" s="2">
+        <v>0.49</v>
+      </c>
+      <c r="K1367" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:11" ht="18">
+      <c r="A1368" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1368" s="6">
+        <v>45931</v>
+      </c>
+      <c r="C1368" s="2">
+        <v>40</v>
+      </c>
+      <c r="D1368" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E1368" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1368" s="2">
+        <v>22</v>
+      </c>
+      <c r="G1368" s="2">
+        <v>38</v>
+      </c>
+      <c r="H1368" s="2">
+        <v>16</v>
+      </c>
+      <c r="I1368" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1368" s="2">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="K1368" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:11" ht="18">
+      <c r="A1369" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1369" s="6">
+        <v>45962</v>
+      </c>
+      <c r="C1369" s="2">
+        <v>66</v>
+      </c>
+      <c r="D1369" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E1369" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1369" s="2">
+        <v>38</v>
+      </c>
+      <c r="G1369" s="2">
+        <v>75</v>
+      </c>
+      <c r="H1369" s="2">
+        <v>17</v>
+      </c>
+      <c r="I1369" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1369" s="2">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="K1369" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:11" ht="18">
+      <c r="A1370" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1370" s="6">
+        <v>45992</v>
+      </c>
+      <c r="C1370" s="2">
+        <v>101</v>
+      </c>
+      <c r="D1370" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E1370" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1370" s="2">
+        <v>73</v>
+      </c>
+      <c r="G1370" s="2">
+        <v>104</v>
+      </c>
+      <c r="H1370" s="2">
+        <v>24</v>
+      </c>
+      <c r="I1370" s="2">
+        <v>6</v>
+      </c>
+      <c r="J1370" s="2">
+        <v>0.68100000000000005</v>
+      </c>
+      <c r="K1370" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:11" ht="18">
+      <c r="A1371" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1371" s="6">
+        <v>46023</v>
+      </c>
+      <c r="C1371" s="2">
+        <v>84</v>
+      </c>
+      <c r="D1371" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E1371" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1371" s="2">
+        <v>61</v>
+      </c>
+      <c r="G1371" s="2">
+        <v>82</v>
+      </c>
+      <c r="H1371" s="2">
+        <v>22</v>
+      </c>
+      <c r="I1371" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1371" s="2">
+        <v>0.623</v>
+      </c>
+      <c r="K1371" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:11" ht="18">
+      <c r="A1372" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1372" s="6">
+        <v>46054</v>
+      </c>
+      <c r="C1372" s="2">
+        <v>74</v>
+      </c>
+      <c r="D1372" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E1372" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1372" s="2">
+        <v>50</v>
+      </c>
+      <c r="G1372" s="2">
+        <v>85</v>
+      </c>
+      <c r="H1372" s="2">
+        <v>15</v>
+      </c>
+      <c r="I1372" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1372" s="2">
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="K1372" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:11" ht="18">
+      <c r="A1373" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1373" s="6">
+        <v>46082</v>
+      </c>
+      <c r="C1373" s="2">
+        <v>89</v>
+      </c>
+      <c r="D1373" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="E1373" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1373" s="2">
+        <v>55</v>
+      </c>
+      <c r="G1373" s="2">
+        <v>79</v>
+      </c>
+      <c r="H1373" s="2">
+        <v>16</v>
+      </c>
+      <c r="I1373" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1373" s="2">
+        <v>0.497</v>
+      </c>
+      <c r="K1373" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:11" ht="18">
+      <c r="A1374" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1374" s="6">
+        <v>46113</v>
+      </c>
+      <c r="C1374" s="2">
+        <v>63</v>
+      </c>
+      <c r="D1374" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E1374" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1374" s="2">
+        <v>24</v>
+      </c>
+      <c r="G1374" s="2">
+        <v>52</v>
+      </c>
+      <c r="H1374" s="2">
+        <v>12</v>
+      </c>
+      <c r="I1374" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1374" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="K1374" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:11" ht="18">
+      <c r="A1375" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B1375" s="6">
+        <v>46143</v>
+      </c>
+      <c r="C1375" s="2">
+        <v>60</v>
+      </c>
+      <c r="D1375" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E1375" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1375" s="2">
+        <v>19</v>
+      </c>
+      <c r="G1375" s="2">
+        <v>34</v>
+      </c>
+      <c r="H1375" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1375" s="2">
+        <v>5</v>
+      </c>
+      <c r="J1375" s="2">
+        <v>0.48099999999999998</v>
+      </c>
+      <c r="K1375" s="2">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -47690,6 +53552,163 @@
     <hyperlink ref="B1216" r:id="rId1215" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E8%8A%9C%E6%B9%96&amp;month=2026-03" xr:uid="{B005A7B6-A64A-2249-B7C9-C1BF1E6A95F4}"/>
     <hyperlink ref="B1217" r:id="rId1216" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E8%8A%9C%E6%B9%96&amp;month=2026-04" xr:uid="{EB2C8D86-F0DF-D243-95B7-EFBC8E53B6AD}"/>
     <hyperlink ref="B1218" r:id="rId1217" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E8%8A%9C%E6%B9%96&amp;month=2026-05" xr:uid="{91CA1834-9FA7-2E43-A696-CB4D860B0817}"/>
+    <hyperlink ref="B1219" r:id="rId1218" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2013-05" xr:uid="{9D99A72B-4CFB-B349-8E68-C8E76331595D}"/>
+    <hyperlink ref="B1220" r:id="rId1219" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2013-06" xr:uid="{B44052F0-927F-FB4A-81D7-EBBF89F8EF70}"/>
+    <hyperlink ref="B1221" r:id="rId1220" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2013-07" xr:uid="{80063626-9D71-BB44-8BCB-42A8905C3E2F}"/>
+    <hyperlink ref="B1222" r:id="rId1221" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2013-08" xr:uid="{43417BAB-285F-6D44-9B5F-99D282F30FDE}"/>
+    <hyperlink ref="B1223" r:id="rId1222" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2013-09" xr:uid="{AF259CF2-6E0D-7540-8298-12422064DC0D}"/>
+    <hyperlink ref="B1224" r:id="rId1223" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2013-10" xr:uid="{C3482372-D91E-6D4D-8452-3991B89EEEF4}"/>
+    <hyperlink ref="B1225" r:id="rId1224" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2013-11" xr:uid="{04D9867A-2D66-D646-A993-890639D53226}"/>
+    <hyperlink ref="B1226" r:id="rId1225" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2013-12" xr:uid="{598E6C1F-F34F-974F-A1D1-0242AD1D8E4A}"/>
+    <hyperlink ref="B1227" r:id="rId1226" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2014-01" xr:uid="{AD9C43FA-5263-F042-924D-65A7230D4FED}"/>
+    <hyperlink ref="B1228" r:id="rId1227" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2014-02" xr:uid="{C315F2EF-770E-8B46-B99C-C750CCC2179C}"/>
+    <hyperlink ref="B1229" r:id="rId1228" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2014-03" xr:uid="{D8A2E833-65C8-934F-BFF8-F7A00B003382}"/>
+    <hyperlink ref="B1230" r:id="rId1229" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2014-04" xr:uid="{E7C802AE-F3BE-D84E-94DB-B5E41D4D5258}"/>
+    <hyperlink ref="B1231" r:id="rId1230" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2014-05" xr:uid="{ACFE94E6-57D2-8842-B15D-7A9B779D21BE}"/>
+    <hyperlink ref="B1232" r:id="rId1231" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2014-06" xr:uid="{DCC971BE-392F-754C-8E52-847C8210D235}"/>
+    <hyperlink ref="B1233" r:id="rId1232" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2014-07" xr:uid="{8A35DB90-E2FF-E04C-8EAB-9C91A0BE73DC}"/>
+    <hyperlink ref="B1234" r:id="rId1233" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2014-08" xr:uid="{10C3319F-23A9-4849-BA72-539D829AF905}"/>
+    <hyperlink ref="B1235" r:id="rId1234" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2014-09" xr:uid="{7CB6C787-0BAB-A14A-BCDF-4178C4B75996}"/>
+    <hyperlink ref="B1236" r:id="rId1235" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2014-10" xr:uid="{B8182428-A6D8-6A4A-B4B2-4AE688200419}"/>
+    <hyperlink ref="B1237" r:id="rId1236" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2014-11" xr:uid="{3AAD9E35-F327-0F4E-907C-579B970794CA}"/>
+    <hyperlink ref="B1238" r:id="rId1237" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2014-12" xr:uid="{9868D1AE-C888-9E45-99F9-86B56ADE8300}"/>
+    <hyperlink ref="B1239" r:id="rId1238" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2015-01" xr:uid="{76274394-4398-D848-BBAF-24AD8386FDE3}"/>
+    <hyperlink ref="B1240" r:id="rId1239" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2015-02" xr:uid="{F606214F-6FFC-584D-ACA3-9523E2FEDCED}"/>
+    <hyperlink ref="B1241" r:id="rId1240" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2015-03" xr:uid="{BE469DC0-1774-8D44-9F1B-E653673DFC26}"/>
+    <hyperlink ref="B1242" r:id="rId1241" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2015-04" xr:uid="{0C41D9F8-51D3-334F-B3DF-89AFFCCB7ECA}"/>
+    <hyperlink ref="B1243" r:id="rId1242" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2015-05" xr:uid="{ECE2771D-1710-0248-95EC-DA8564632F4E}"/>
+    <hyperlink ref="B1244" r:id="rId1243" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2015-06" xr:uid="{42A3E26A-0D57-2044-BDF6-A0FB97EA0BF5}"/>
+    <hyperlink ref="B1245" r:id="rId1244" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2015-07" xr:uid="{E72F951F-7958-3941-BBE9-DA2B8C59B0BD}"/>
+    <hyperlink ref="B1246" r:id="rId1245" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2015-08" xr:uid="{87028FBA-E2E5-654B-86C8-44820A5419D7}"/>
+    <hyperlink ref="B1247" r:id="rId1246" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2015-09" xr:uid="{A94F0768-1705-A14C-844F-BF3BDBB7FD14}"/>
+    <hyperlink ref="B1248" r:id="rId1247" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2015-10" xr:uid="{C604F1A5-2E49-B845-940C-BB786FD7F4C0}"/>
+    <hyperlink ref="B1249" r:id="rId1248" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2015-11" xr:uid="{8E082498-4803-5D47-882A-6D632F906295}"/>
+    <hyperlink ref="B1250" r:id="rId1249" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2015-12" xr:uid="{FC6C3AFC-E0B1-9745-9463-37047B498693}"/>
+    <hyperlink ref="B1251" r:id="rId1250" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2016-01" xr:uid="{001AC933-DFB3-804B-A6E7-E94EA6BA2EE6}"/>
+    <hyperlink ref="B1252" r:id="rId1251" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2016-02" xr:uid="{197C1A7B-4BCA-564D-9D38-1FECFA6328D8}"/>
+    <hyperlink ref="B1253" r:id="rId1252" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2016-03" xr:uid="{CAB7A801-48E1-CF4C-9E25-92A7EAAD0248}"/>
+    <hyperlink ref="B1254" r:id="rId1253" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2016-04" xr:uid="{66A99DCC-A39A-6A4B-92E0-73976461150C}"/>
+    <hyperlink ref="B1255" r:id="rId1254" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2016-05" xr:uid="{1790699F-34C0-0649-99D9-272BCC01CD03}"/>
+    <hyperlink ref="B1256" r:id="rId1255" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2016-06" xr:uid="{816ECE99-0230-7744-BD68-2DE15BDA5230}"/>
+    <hyperlink ref="B1257" r:id="rId1256" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2016-07" xr:uid="{2427DA80-D27F-ED4C-905A-3C4F84CED509}"/>
+    <hyperlink ref="B1258" r:id="rId1257" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2016-08" xr:uid="{28E10F49-4714-E343-9E75-99AC5B56A218}"/>
+    <hyperlink ref="B1259" r:id="rId1258" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2016-09" xr:uid="{26531BA0-AEE1-BB49-912C-E68694219B74}"/>
+    <hyperlink ref="B1260" r:id="rId1259" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2016-10" xr:uid="{6AA79164-C378-884B-88B9-CC8628C3019C}"/>
+    <hyperlink ref="B1261" r:id="rId1260" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2016-11" xr:uid="{B8C816A6-F017-2E4F-A032-351ED1B5482C}"/>
+    <hyperlink ref="B1262" r:id="rId1261" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2016-12" xr:uid="{2858B01A-1CF6-524C-B467-F46B76A86C26}"/>
+    <hyperlink ref="B1263" r:id="rId1262" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2017-01" xr:uid="{6D2FF43E-CEC1-254F-8F36-2964C67D3CCE}"/>
+    <hyperlink ref="B1264" r:id="rId1263" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2017-02" xr:uid="{DAD611C8-C145-294F-9ED4-190CA683F35A}"/>
+    <hyperlink ref="B1265" r:id="rId1264" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2017-03" xr:uid="{9FE9FCE5-EC8D-954B-ACA0-5FD2A2B11406}"/>
+    <hyperlink ref="B1266" r:id="rId1265" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2017-04" xr:uid="{8C610A1C-0E46-F840-82B1-BACADF7EFD9C}"/>
+    <hyperlink ref="B1267" r:id="rId1266" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2017-05" xr:uid="{BA0310B5-FC05-F04A-B26B-BE18AED82FF7}"/>
+    <hyperlink ref="B1268" r:id="rId1267" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2017-06" xr:uid="{B77851CA-943E-C346-81DD-C429EC637484}"/>
+    <hyperlink ref="B1269" r:id="rId1268" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2017-07" xr:uid="{3DC06BAB-7F3C-394D-9E25-6A981EE95356}"/>
+    <hyperlink ref="B1270" r:id="rId1269" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2017-08" xr:uid="{5DD533AC-27CD-0246-A1D0-F2CBA541E39C}"/>
+    <hyperlink ref="B1271" r:id="rId1270" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2017-09" xr:uid="{0E669287-C33B-CB4F-8B7C-1693973D7C47}"/>
+    <hyperlink ref="B1272" r:id="rId1271" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2017-10" xr:uid="{0DB18930-2BD7-8A4E-9B32-A9EE9AFA759F}"/>
+    <hyperlink ref="B1273" r:id="rId1272" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2017-11" xr:uid="{1D3F3E4B-8E33-DA44-A5F9-ADD5EE1C9CA7}"/>
+    <hyperlink ref="B1274" r:id="rId1273" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2017-12" xr:uid="{556FC8D0-A67B-6D4A-9A14-09090F2C0AE2}"/>
+    <hyperlink ref="B1275" r:id="rId1274" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2018-01" xr:uid="{0F6A1C7E-17D3-B944-8227-61BEC5A48E94}"/>
+    <hyperlink ref="B1276" r:id="rId1275" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2018-02" xr:uid="{8A35FCBF-420D-6A4E-AF66-374873033594}"/>
+    <hyperlink ref="B1277" r:id="rId1276" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2018-03" xr:uid="{7D1F5C9C-27FF-1342-AC29-66D4294C972F}"/>
+    <hyperlink ref="B1278" r:id="rId1277" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2018-04" xr:uid="{CDC0B372-9E5A-A747-AEBD-B32F987BD05E}"/>
+    <hyperlink ref="B1279" r:id="rId1278" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2018-05" xr:uid="{A3658C66-996C-934D-A11A-0176E48765C7}"/>
+    <hyperlink ref="B1280" r:id="rId1279" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2018-06" xr:uid="{DE055FE3-A6F6-1F45-8074-2F19E2E394E2}"/>
+    <hyperlink ref="B1281" r:id="rId1280" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2018-07" xr:uid="{6943280E-335D-6F40-BBE4-D5A07AF8EC7B}"/>
+    <hyperlink ref="B1282" r:id="rId1281" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2018-08" xr:uid="{CD4B961B-70B5-9648-9F02-94A31051F7CB}"/>
+    <hyperlink ref="B1283" r:id="rId1282" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2018-09" xr:uid="{C8D137EF-7A59-CF41-A476-8AEA5D0FD593}"/>
+    <hyperlink ref="B1284" r:id="rId1283" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2018-10" xr:uid="{5DB87933-7088-9C49-86EA-8F973E0BB25A}"/>
+    <hyperlink ref="B1285" r:id="rId1284" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2018-11" xr:uid="{4744062B-A998-E14F-B326-CD6DF4D03589}"/>
+    <hyperlink ref="B1286" r:id="rId1285" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2018-12" xr:uid="{9BD0EDB2-54A4-1440-9E0B-0327369A35AF}"/>
+    <hyperlink ref="B1287" r:id="rId1286" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2019-01" xr:uid="{B2527E78-450E-0745-AEFF-C2566D48DC23}"/>
+    <hyperlink ref="B1288" r:id="rId1287" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2019-02" xr:uid="{86FDF655-4588-F04B-B834-028ED1FBB0D3}"/>
+    <hyperlink ref="B1289" r:id="rId1288" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2019-03" xr:uid="{F86C4804-F228-A24A-9B76-512D0A912DCF}"/>
+    <hyperlink ref="B1290" r:id="rId1289" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2019-04" xr:uid="{EA8489D8-2E04-0A49-9642-AE346118609A}"/>
+    <hyperlink ref="B1291" r:id="rId1290" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2019-05" xr:uid="{6A8422A7-FB19-114A-8128-F78E1483FF79}"/>
+    <hyperlink ref="B1292" r:id="rId1291" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2019-06" xr:uid="{7AA22FD8-8E70-CD47-B198-CECC67C279FF}"/>
+    <hyperlink ref="B1293" r:id="rId1292" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2019-07" xr:uid="{BEE626DC-A9AF-5844-82F3-4C17A2D50109}"/>
+    <hyperlink ref="B1294" r:id="rId1293" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2019-08" xr:uid="{D73AF6F8-8BCE-2F48-B6E1-C892431A720C}"/>
+    <hyperlink ref="B1295" r:id="rId1294" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2019-09" xr:uid="{5AA2084A-A328-2545-811A-3BF7E8036EFA}"/>
+    <hyperlink ref="B1296" r:id="rId1295" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2019-10" xr:uid="{6015C741-E86D-B04F-8E3C-3219DD281A28}"/>
+    <hyperlink ref="B1297" r:id="rId1296" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2019-11" xr:uid="{220E307E-3ECA-CA4A-B488-48ACF4827512}"/>
+    <hyperlink ref="B1298" r:id="rId1297" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2019-12" xr:uid="{17C13D55-322F-C94F-BCBB-E23012124F2A}"/>
+    <hyperlink ref="B1299" r:id="rId1298" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2020-01" xr:uid="{32C31E71-6171-804E-9138-ABEA80045AB1}"/>
+    <hyperlink ref="B1300" r:id="rId1299" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2020-02" xr:uid="{6A4DC1EF-F245-064F-9187-88E27BD2F914}"/>
+    <hyperlink ref="B1301" r:id="rId1300" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2020-03" xr:uid="{9E17EB2D-28FA-DD45-ABC9-A3955BC1AB30}"/>
+    <hyperlink ref="B1302" r:id="rId1301" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2020-04" xr:uid="{6D8E38C9-F2E5-8349-B91A-456E061F1699}"/>
+    <hyperlink ref="B1303" r:id="rId1302" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2020-05" xr:uid="{D02FB327-2940-314C-B35F-4CAD8FC57A44}"/>
+    <hyperlink ref="B1304" r:id="rId1303" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2020-06" xr:uid="{DE4B9BED-FEA3-C640-9578-90818A7253DC}"/>
+    <hyperlink ref="B1305" r:id="rId1304" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2020-07" xr:uid="{9D087B3D-F2A6-CC4E-9994-365622B9501C}"/>
+    <hyperlink ref="B1306" r:id="rId1305" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2020-08" xr:uid="{C07010F3-3E31-AC4A-80DE-E34A176FCFBA}"/>
+    <hyperlink ref="B1307" r:id="rId1306" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2020-09" xr:uid="{E24A4C1A-0E1A-3E4C-8241-76FBFF1A42DF}"/>
+    <hyperlink ref="B1308" r:id="rId1307" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2020-10" xr:uid="{E10E3811-D478-3441-AE0C-9C3ADAD31EC4}"/>
+    <hyperlink ref="B1309" r:id="rId1308" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2020-11" xr:uid="{3497EBC4-5C16-CC4F-B248-1ED8A4F398E8}"/>
+    <hyperlink ref="B1310" r:id="rId1309" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2020-12" xr:uid="{6CFBEBA0-47FA-4643-B1EB-49CE5C71DF83}"/>
+    <hyperlink ref="B1311" r:id="rId1310" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2021-01" xr:uid="{2E300B74-F749-0540-86E0-F3687306B9F7}"/>
+    <hyperlink ref="B1312" r:id="rId1311" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2021-02" xr:uid="{D566C43F-D9C0-5545-8BDB-050DBE2B660C}"/>
+    <hyperlink ref="B1313" r:id="rId1312" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2021-03" xr:uid="{F49DC6AB-8789-B746-A5D9-CBE754AD4D3D}"/>
+    <hyperlink ref="B1314" r:id="rId1313" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2021-04" xr:uid="{BFFB040B-6DA9-8C44-BDBA-44AED418F8C7}"/>
+    <hyperlink ref="B1315" r:id="rId1314" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2021-05" xr:uid="{44C7693A-3C78-C947-9CCF-AAF3EDCB2C35}"/>
+    <hyperlink ref="B1316" r:id="rId1315" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2021-06" xr:uid="{26553977-AD54-6642-BCBC-EE30047061DE}"/>
+    <hyperlink ref="B1317" r:id="rId1316" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2021-07" xr:uid="{4BCC5AC9-2FDD-314A-9D2D-2B2B9883D574}"/>
+    <hyperlink ref="B1318" r:id="rId1317" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2021-08" xr:uid="{A594E74A-F324-C946-B866-E882C01BE48C}"/>
+    <hyperlink ref="B1319" r:id="rId1318" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2021-09" xr:uid="{80F6BA6A-D49F-C343-8244-8773878248A4}"/>
+    <hyperlink ref="B1320" r:id="rId1319" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2021-10" xr:uid="{D43311B7-F36C-BA4D-AB9C-C086E67AFC55}"/>
+    <hyperlink ref="B1321" r:id="rId1320" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2021-11" xr:uid="{49B14603-7627-8847-AD94-F68F1BC6FA70}"/>
+    <hyperlink ref="B1322" r:id="rId1321" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2021-12" xr:uid="{2D914583-AD39-974C-A894-4CD60E21FA3B}"/>
+    <hyperlink ref="B1323" r:id="rId1322" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2022-01" xr:uid="{5587EBE4-B42E-684F-9F3F-5F055F96EC19}"/>
+    <hyperlink ref="B1324" r:id="rId1323" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2022-02" xr:uid="{69FB922B-1F45-924D-8499-7B46CC72070F}"/>
+    <hyperlink ref="B1325" r:id="rId1324" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2022-03" xr:uid="{821D1DCE-0780-F742-ABA2-2594FB476C36}"/>
+    <hyperlink ref="B1326" r:id="rId1325" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2022-04" xr:uid="{113C8136-E6CB-584B-9D74-531401B42603}"/>
+    <hyperlink ref="B1327" r:id="rId1326" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2022-05" xr:uid="{D3563149-83BD-A74C-93AC-5FBAFAEB0EF9}"/>
+    <hyperlink ref="B1328" r:id="rId1327" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2022-06" xr:uid="{06B9DD6D-EBBD-1847-9FC8-EEA1D9BAE221}"/>
+    <hyperlink ref="B1329" r:id="rId1328" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2022-07" xr:uid="{24A6DA98-C840-5A46-A967-F00BB63E61C0}"/>
+    <hyperlink ref="B1330" r:id="rId1329" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2022-08" xr:uid="{A4385BC1-AE14-B340-BA53-57E1D46F070B}"/>
+    <hyperlink ref="B1331" r:id="rId1330" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2022-09" xr:uid="{13FE61E4-F3FF-4D44-8739-CA831348AC55}"/>
+    <hyperlink ref="B1332" r:id="rId1331" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2022-10" xr:uid="{E8C99B12-E629-9847-A477-B95BF0E60F2C}"/>
+    <hyperlink ref="B1333" r:id="rId1332" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2022-11" xr:uid="{954C01F0-02A5-FC43-9661-FD1585620314}"/>
+    <hyperlink ref="B1334" r:id="rId1333" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2022-12" xr:uid="{FF577186-B0EB-D64D-92D9-2DA9A24319EF}"/>
+    <hyperlink ref="B1335" r:id="rId1334" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2023-01" xr:uid="{43BB3EC5-57F0-2A43-B4A1-2863106C5646}"/>
+    <hyperlink ref="B1336" r:id="rId1335" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2023-02" xr:uid="{0FD94A3A-1F41-F143-871D-22B59D883061}"/>
+    <hyperlink ref="B1337" r:id="rId1336" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2023-03" xr:uid="{9F24AADF-B278-2D46-85AB-E8B2A153DCCD}"/>
+    <hyperlink ref="B1338" r:id="rId1337" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2023-04" xr:uid="{F307F859-754E-EB4C-B073-0D2A2D2DEE52}"/>
+    <hyperlink ref="B1339" r:id="rId1338" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2023-05" xr:uid="{FFEA4BED-2E80-784A-86A4-8193A1857586}"/>
+    <hyperlink ref="B1340" r:id="rId1339" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2023-06" xr:uid="{46428229-7C46-C545-B3CE-53A3704EC585}"/>
+    <hyperlink ref="B1341" r:id="rId1340" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2023-07" xr:uid="{85653EE8-1A44-0644-8C8A-F3F3E1286327}"/>
+    <hyperlink ref="B1342" r:id="rId1341" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2023-08" xr:uid="{A5CFBFBC-EA31-F545-BDE8-CFF2EB4492A1}"/>
+    <hyperlink ref="B1343" r:id="rId1342" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2023-09" xr:uid="{6273AEC1-A4FC-9D47-A4FA-14BA11967939}"/>
+    <hyperlink ref="B1344" r:id="rId1343" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2023-10" xr:uid="{602210DF-6808-B34B-8C99-8D6623F8E362}"/>
+    <hyperlink ref="B1345" r:id="rId1344" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2023-11" xr:uid="{F276653A-3438-344B-A550-2FADED296B3C}"/>
+    <hyperlink ref="B1346" r:id="rId1345" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2023-12" xr:uid="{FAA6FCEE-6879-0D4B-9207-B1A5B71A38B5}"/>
+    <hyperlink ref="B1347" r:id="rId1346" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2024-01" xr:uid="{4714B316-59D2-7A41-9BA3-3DCE8AEDE9EB}"/>
+    <hyperlink ref="B1348" r:id="rId1347" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2024-02" xr:uid="{F4445464-C123-CF42-BA97-EB44D495B4CA}"/>
+    <hyperlink ref="B1349" r:id="rId1348" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2024-03" xr:uid="{A38E9613-07FC-A548-B9CD-BD891B27B488}"/>
+    <hyperlink ref="B1350" r:id="rId1349" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2024-04" xr:uid="{69082133-47BE-ED46-92E1-75E896DBA786}"/>
+    <hyperlink ref="B1351" r:id="rId1350" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2024-05" xr:uid="{7554E36C-8C9F-BF40-B7CD-CFF3776FD804}"/>
+    <hyperlink ref="B1352" r:id="rId1351" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2024-06" xr:uid="{56175A25-850B-034A-ABA9-BA99B9926A9C}"/>
+    <hyperlink ref="B1353" r:id="rId1352" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2024-07" xr:uid="{C46DB7A8-CC8E-A542-B325-98119F0F2FD7}"/>
+    <hyperlink ref="B1354" r:id="rId1353" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2024-08" xr:uid="{BCD5CA77-5E0F-BA43-B62E-BE620C1534C6}"/>
+    <hyperlink ref="B1355" r:id="rId1354" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2024-09" xr:uid="{03FCB02F-A054-9841-99C9-E9431FCF632E}"/>
+    <hyperlink ref="B1356" r:id="rId1355" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2024-10" xr:uid="{642F4D7D-6BC9-C342-BEFA-7057846D6644}"/>
+    <hyperlink ref="B1357" r:id="rId1356" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2024-11" xr:uid="{89E27782-872A-D24F-895C-658EC008AECD}"/>
+    <hyperlink ref="B1358" r:id="rId1357" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2024-12" xr:uid="{E4E86916-207A-F945-87B1-06702E1C309C}"/>
+    <hyperlink ref="B1359" r:id="rId1358" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2025-01" xr:uid="{8A134779-ABAF-BC4C-AF07-8FB089686B55}"/>
+    <hyperlink ref="B1360" r:id="rId1359" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2025-02" xr:uid="{9FC90B0A-8C05-9743-A394-300333B9917E}"/>
+    <hyperlink ref="B1361" r:id="rId1360" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2025-03" xr:uid="{E5CD5BF7-B6C9-B24C-A07B-3FEAF52A9607}"/>
+    <hyperlink ref="B1362" r:id="rId1361" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2025-04" xr:uid="{7C5C305A-E094-2C44-9172-A86D2ED79FD4}"/>
+    <hyperlink ref="B1363" r:id="rId1362" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2025-05" xr:uid="{324D3DA4-AC0B-D640-A1EF-4C5AD116745F}"/>
+    <hyperlink ref="B1364" r:id="rId1363" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2025-06" xr:uid="{6F994DD8-A7A2-A641-A423-2C80040064A2}"/>
+    <hyperlink ref="B1365" r:id="rId1364" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2025-07" xr:uid="{8259034B-020C-5441-88DD-89519236F3A3}"/>
+    <hyperlink ref="B1366" r:id="rId1365" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2025-08" xr:uid="{75F06C8F-5625-FC4B-A79B-D7D79445EC9F}"/>
+    <hyperlink ref="B1367" r:id="rId1366" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2025-09" xr:uid="{68EC5BBA-47F3-A94D-94E6-3758CB720847}"/>
+    <hyperlink ref="B1368" r:id="rId1367" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2025-10" xr:uid="{C9F64112-2607-9D4A-BEF1-6BA2E49F8813}"/>
+    <hyperlink ref="B1369" r:id="rId1368" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2025-11" xr:uid="{3ECF6CFF-83F1-0944-AB08-255B290CBA0F}"/>
+    <hyperlink ref="B1370" r:id="rId1369" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2025-12" xr:uid="{E24903AD-A494-FB40-AB63-33D3B406DC60}"/>
+    <hyperlink ref="B1371" r:id="rId1370" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2026-01" xr:uid="{791D6AD9-FC40-804C-9D73-D66D2C9F248D}"/>
+    <hyperlink ref="B1372" r:id="rId1371" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2026-02" xr:uid="{7FD2BB2F-43D1-8244-BF82-A58D2467BC66}"/>
+    <hyperlink ref="B1373" r:id="rId1372" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2026-03" xr:uid="{87BF79E1-B258-7342-92CE-D37656488516}"/>
+    <hyperlink ref="B1374" r:id="rId1373" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2026-04" xr:uid="{17EE604B-9A91-1E49-BBEA-369304570D2B}"/>
+    <hyperlink ref="B1375" r:id="rId1374" display="https://www.aqistudy.cn/historydata/daydata.php?city=%E4%BF%A1%E9%98%B3&amp;month=2026-05" xr:uid="{AB9F351D-AA2C-734F-B6EF-EE61E1D591FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
